--- a/SCH-STH/Impact assessments/Senegal/2025/november/sn_sppa_impact_2511_1_site.xlsx
+++ b/SCH-STH/Impact assessments/Senegal/2025/november/sn_sppa_impact_2511_1_site.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\SCH-STH\Impact assessments\Senegal\2025\november\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3314DC74-89E6-4C60-A25A-6964C65182C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{249D69AE-C32E-4C55-BCC0-FC30B51DF225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="498" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1232,9 +1232,6 @@
     <t>PS SANDIAL</t>
   </si>
   <si>
-    <t>PS SERVICE D'HYGIENE</t>
-  </si>
-  <si>
     <t>PS ST LAURENT</t>
   </si>
   <si>
@@ -1805,9 +1802,6 @@
     <t>OUMAR HAMET WANE</t>
   </si>
   <si>
-    <t>EP ALLOUWA D'OR</t>
-  </si>
-  <si>
     <t>EL HADJI BASSIROU DIAGNE(GIBRALTAR 2)</t>
   </si>
   <si>
@@ -1905,6 +1899,12 @@
   </si>
   <si>
     <t>EFA TOUBA ROFF</t>
+  </si>
+  <si>
+    <t>PS SERVICE D.HYGIENE</t>
+  </si>
+  <si>
+    <t>EP ALLOUWA D.OR</t>
   </si>
 </sst>
 </file>
@@ -6060,10 +6060,10 @@
         <v>33</v>
       </c>
       <c r="B170" s="22" t="s">
-        <v>351</v>
+        <v>574</v>
       </c>
       <c r="C170" s="22" t="s">
-        <v>351</v>
+        <v>574</v>
       </c>
       <c r="D170" s="22"/>
       <c r="E170" s="19" t="s">
@@ -6075,10 +6075,10 @@
         <v>33</v>
       </c>
       <c r="B171" s="22" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C171" s="22" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D171" s="22"/>
       <c r="E171" s="19" t="s">
@@ -6090,10 +6090,10 @@
         <v>33</v>
       </c>
       <c r="B172" s="22" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C172" s="22" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D172" s="22"/>
       <c r="E172" s="19" t="s">
@@ -6105,10 +6105,10 @@
         <v>33</v>
       </c>
       <c r="B173" s="22" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C173" s="22" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D173" s="22"/>
       <c r="E173" s="19" t="s">
@@ -6120,10 +6120,10 @@
         <v>33</v>
       </c>
       <c r="B174" s="22" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C174" s="22" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D174" s="22"/>
       <c r="E174" s="19" t="s">
@@ -6135,10 +6135,10 @@
         <v>33</v>
       </c>
       <c r="B175" s="22" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C175" s="22" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D175" s="22"/>
       <c r="E175" s="19" t="s">
@@ -6150,10 +6150,10 @@
         <v>33</v>
       </c>
       <c r="B176" s="22" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C176" s="22" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D176" s="22"/>
       <c r="E176" s="19" t="s">
@@ -6165,10 +6165,10 @@
         <v>33</v>
       </c>
       <c r="B177" s="22" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C177" s="22" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D177" s="22"/>
       <c r="E177" s="19" t="s">
@@ -6180,10 +6180,10 @@
         <v>33</v>
       </c>
       <c r="B178" s="22" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C178" s="22" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D178" s="22"/>
       <c r="E178" s="19" t="s">
@@ -6195,10 +6195,10 @@
         <v>33</v>
       </c>
       <c r="B179" s="22" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C179" s="22" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D179" s="22"/>
       <c r="E179" s="19" t="s">
@@ -6210,10 +6210,10 @@
         <v>33</v>
       </c>
       <c r="B180" s="22" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C180" s="22" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D180" s="22"/>
       <c r="E180" s="19" t="s">
@@ -6225,10 +6225,10 @@
         <v>33</v>
       </c>
       <c r="B181" s="22" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C181" s="22" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D181" s="22"/>
       <c r="E181" s="19" t="s">
@@ -6240,10 +6240,10 @@
         <v>33</v>
       </c>
       <c r="B182" s="22" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C182" s="22" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D182" s="22"/>
       <c r="E182" s="19" t="s">
@@ -6255,10 +6255,10 @@
         <v>33</v>
       </c>
       <c r="B183" s="22" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C183" s="22" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D183" s="22"/>
       <c r="E183" s="19" t="s">
@@ -6270,10 +6270,10 @@
         <v>33</v>
       </c>
       <c r="B184" s="22" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C184" s="22" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D184" s="22"/>
       <c r="E184" s="19" t="s">
@@ -6285,10 +6285,10 @@
         <v>33</v>
       </c>
       <c r="B185" s="22" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C185" s="22" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D185" s="22"/>
       <c r="E185" s="19" t="s">
@@ -6300,10 +6300,10 @@
         <v>33</v>
       </c>
       <c r="B186" s="22" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C186" s="22" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D186" s="22"/>
       <c r="E186" s="19" t="s">
@@ -6315,10 +6315,10 @@
         <v>33</v>
       </c>
       <c r="B187" s="22" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C187" s="22" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D187" s="22"/>
       <c r="E187" s="19" t="s">
@@ -6330,10 +6330,10 @@
         <v>33</v>
       </c>
       <c r="B188" s="22" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C188" s="22" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D188" s="22"/>
       <c r="E188" s="19" t="s">
@@ -6345,10 +6345,10 @@
         <v>33</v>
       </c>
       <c r="B189" s="22" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C189" s="22" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D189" s="22"/>
       <c r="E189" s="19" t="s">
@@ -6360,10 +6360,10 @@
         <v>33</v>
       </c>
       <c r="B190" s="22" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C190" s="22" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D190" s="22"/>
       <c r="E190" s="19" t="s">
@@ -6375,10 +6375,10 @@
         <v>33</v>
       </c>
       <c r="B191" s="22" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C191" s="22" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D191" s="22"/>
       <c r="E191" s="19" t="s">
@@ -6390,10 +6390,10 @@
         <v>33</v>
       </c>
       <c r="B192" s="22" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C192" s="22" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D192" s="22"/>
       <c r="E192" s="19" t="s">
@@ -6405,10 +6405,10 @@
         <v>33</v>
       </c>
       <c r="B193" s="22" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C193" s="22" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D193" s="22"/>
       <c r="E193" s="19" t="s">
@@ -6420,10 +6420,10 @@
         <v>33</v>
       </c>
       <c r="B194" s="22" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C194" s="22" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D194" s="22"/>
       <c r="E194" s="19" t="s">
@@ -6435,10 +6435,10 @@
         <v>33</v>
       </c>
       <c r="B195" s="22" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C195" s="22" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D195" s="22"/>
       <c r="E195" s="19" t="s">
@@ -6450,10 +6450,10 @@
         <v>33</v>
       </c>
       <c r="B196" s="22" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C196" s="22" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D196" s="22"/>
       <c r="E196" s="19" t="s">
@@ -6465,10 +6465,10 @@
         <v>33</v>
       </c>
       <c r="B197" s="22" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C197" s="22" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D197" s="22"/>
       <c r="E197" s="19" t="s">
@@ -6480,10 +6480,10 @@
         <v>33</v>
       </c>
       <c r="B198" s="22" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C198" s="22" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D198" s="22"/>
       <c r="E198" s="19" t="s">
@@ -6495,10 +6495,10 @@
         <v>33</v>
       </c>
       <c r="B199" s="22" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C199" s="22" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D199" s="22"/>
       <c r="E199" s="19" t="s">
@@ -6510,10 +6510,10 @@
         <v>33</v>
       </c>
       <c r="B200" s="22" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C200" s="22" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D200" s="22"/>
       <c r="E200" s="19" t="s">
@@ -6525,10 +6525,10 @@
         <v>33</v>
       </c>
       <c r="B201" s="22" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C201" s="22" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D201" s="22"/>
       <c r="E201" s="19" t="s">
@@ -6540,10 +6540,10 @@
         <v>33</v>
       </c>
       <c r="B202" s="22" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C202" s="22" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D202" s="22"/>
       <c r="E202" s="19" t="s">
@@ -6555,10 +6555,10 @@
         <v>33</v>
       </c>
       <c r="B203" s="22" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C203" s="22" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D203" s="22"/>
       <c r="E203" s="19" t="s">
@@ -6570,10 +6570,10 @@
         <v>33</v>
       </c>
       <c r="B204" s="22" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C204" s="22" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D204" s="22"/>
       <c r="E204" s="19" t="s">
@@ -6585,10 +6585,10 @@
         <v>33</v>
       </c>
       <c r="B205" s="22" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C205" s="22" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D205" s="22"/>
       <c r="E205" s="19" t="s">
@@ -6600,10 +6600,10 @@
         <v>33</v>
       </c>
       <c r="B206" s="22" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C206" s="22" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D206" s="22"/>
       <c r="E206" s="19" t="s">
@@ -6615,10 +6615,10 @@
         <v>33</v>
       </c>
       <c r="B207" s="22" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C207" s="22" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D207" s="22"/>
       <c r="E207" s="19" t="s">
@@ -6630,10 +6630,10 @@
         <v>33</v>
       </c>
       <c r="B208" s="22" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C208" s="22" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D208" s="22"/>
       <c r="E208" s="19" t="s">
@@ -6645,10 +6645,10 @@
         <v>33</v>
       </c>
       <c r="B209" s="22" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C209" s="22" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D209" s="22"/>
       <c r="E209" s="19" t="s">
@@ -6660,10 +6660,10 @@
         <v>33</v>
       </c>
       <c r="B210" s="22" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C210" s="22" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D210" s="22"/>
       <c r="E210" s="19" t="s">
@@ -6675,10 +6675,10 @@
         <v>33</v>
       </c>
       <c r="B211" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C211" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D211" s="22"/>
       <c r="E211" s="19" t="s">
@@ -6690,10 +6690,10 @@
         <v>33</v>
       </c>
       <c r="B212" s="22" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C212" s="22" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D212" s="22"/>
       <c r="E212" s="19" t="s">
@@ -6705,10 +6705,10 @@
         <v>33</v>
       </c>
       <c r="B213" s="22" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C213" s="22" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D213" s="22"/>
       <c r="E213" s="19" t="s">
@@ -6720,10 +6720,10 @@
         <v>33</v>
       </c>
       <c r="B214" s="22" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C214" s="22" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D214" s="22"/>
       <c r="E214" s="19" t="s">
@@ -6735,10 +6735,10 @@
         <v>33</v>
       </c>
       <c r="B215" s="22" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C215" s="22" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D215" s="22"/>
       <c r="E215" s="19" t="s">
@@ -6750,10 +6750,10 @@
         <v>33</v>
       </c>
       <c r="B216" s="22" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C216" s="22" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D216" s="22"/>
       <c r="E216" s="19" t="s">
@@ -6765,10 +6765,10 @@
         <v>33</v>
       </c>
       <c r="B217" s="22" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C217" s="22" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D217" s="22"/>
       <c r="E217" s="19" t="s">
@@ -6780,10 +6780,10 @@
         <v>33</v>
       </c>
       <c r="B218" s="22" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C218" s="22" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D218" s="22"/>
       <c r="E218" s="19" t="s">
@@ -6795,10 +6795,10 @@
         <v>33</v>
       </c>
       <c r="B219" s="22" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C219" s="22" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D219" s="22"/>
       <c r="E219" s="19" t="s">
@@ -6810,10 +6810,10 @@
         <v>33</v>
       </c>
       <c r="B220" s="22" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C220" s="22" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D220" s="22"/>
       <c r="E220" s="19" t="s">
@@ -6825,10 +6825,10 @@
         <v>33</v>
       </c>
       <c r="B221" s="22" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C221" s="22" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D221" s="22"/>
       <c r="E221" s="19" t="s">
@@ -6840,10 +6840,10 @@
         <v>33</v>
       </c>
       <c r="B222" s="22" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C222" s="22" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D222" s="22"/>
       <c r="E222" s="19" t="s">
@@ -6855,10 +6855,10 @@
         <v>33</v>
       </c>
       <c r="B223" s="22" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C223" s="22" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D223" s="22"/>
       <c r="E223" s="19" t="s">
@@ -6870,10 +6870,10 @@
         <v>33</v>
       </c>
       <c r="B224" s="22" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C224" s="22" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D224" s="22"/>
       <c r="E224" s="19" t="s">
@@ -6885,10 +6885,10 @@
         <v>33</v>
       </c>
       <c r="B225" s="22" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C225" s="22" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D225" s="22"/>
       <c r="E225" s="19" t="s">
@@ -6900,10 +6900,10 @@
         <v>33</v>
       </c>
       <c r="B226" s="22" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C226" s="22" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D226" s="22"/>
       <c r="E226" s="19" t="s">
@@ -6915,10 +6915,10 @@
         <v>33</v>
       </c>
       <c r="B227" s="22" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C227" s="22" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D227" s="22"/>
       <c r="E227" s="19" t="s">
@@ -6930,10 +6930,10 @@
         <v>33</v>
       </c>
       <c r="B228" s="22" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C228" s="22" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D228" s="22"/>
       <c r="E228" s="19" t="s">
@@ -6945,10 +6945,10 @@
         <v>33</v>
       </c>
       <c r="B229" s="22" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C229" s="22" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D229" s="22"/>
       <c r="E229" s="19" t="s">
@@ -6960,10 +6960,10 @@
         <v>33</v>
       </c>
       <c r="B230" s="22" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C230" s="22" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D230" s="22"/>
       <c r="E230" s="19" t="s">
@@ -6975,10 +6975,10 @@
         <v>33</v>
       </c>
       <c r="B231" s="22" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C231" s="22" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D231" s="22"/>
       <c r="E231" s="19" t="s">
@@ -6990,10 +6990,10 @@
         <v>33</v>
       </c>
       <c r="B232" s="22" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C232" s="22" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D232" s="22"/>
       <c r="E232" s="19" t="s">
@@ -7005,10 +7005,10 @@
         <v>33</v>
       </c>
       <c r="B233" s="22" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C233" s="22" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D233" s="22"/>
       <c r="E233" s="19" t="s">
@@ -7020,10 +7020,10 @@
         <v>33</v>
       </c>
       <c r="B234" s="22" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C234" s="22" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D234" s="22"/>
       <c r="E234" s="19" t="s">
@@ -7035,10 +7035,10 @@
         <v>33</v>
       </c>
       <c r="B235" s="22" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C235" s="22" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D235" s="22"/>
       <c r="E235" s="19" t="s">
@@ -7050,10 +7050,10 @@
         <v>33</v>
       </c>
       <c r="B236" s="22" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C236" s="22" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D236" s="22"/>
       <c r="E236" s="19" t="s">
@@ -7065,10 +7065,10 @@
         <v>33</v>
       </c>
       <c r="B237" s="22" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C237" s="22" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D237" s="22"/>
       <c r="E237" s="19" t="s">
@@ -7080,10 +7080,10 @@
         <v>33</v>
       </c>
       <c r="B238" s="22" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C238" s="22" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D238" s="22"/>
       <c r="E238" s="19" t="s">
@@ -7095,10 +7095,10 @@
         <v>33</v>
       </c>
       <c r="B239" s="22" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C239" s="22" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D239" s="22"/>
       <c r="E239" s="19" t="s">
@@ -7110,10 +7110,10 @@
         <v>33</v>
       </c>
       <c r="B240" s="22" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C240" s="22" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D240" s="22"/>
       <c r="E240" s="19" t="s">
@@ -7125,10 +7125,10 @@
         <v>33</v>
       </c>
       <c r="B241" s="22" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C241" s="22" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D241" s="22"/>
       <c r="E241" s="19" t="s">
@@ -7140,10 +7140,10 @@
         <v>33</v>
       </c>
       <c r="B242" s="22" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C242" s="22" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D242" s="22"/>
       <c r="E242" s="19" t="s">
@@ -7155,10 +7155,10 @@
         <v>33</v>
       </c>
       <c r="B243" s="22" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C243" s="22" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D243" s="22"/>
       <c r="E243" s="19" t="s">
@@ -7170,10 +7170,10 @@
         <v>33</v>
       </c>
       <c r="B244" s="22" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C244" s="22" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D244" s="22"/>
       <c r="E244" s="19" t="s">
@@ -7185,10 +7185,10 @@
         <v>33</v>
       </c>
       <c r="B245" s="22" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C245" s="22" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D245" s="22"/>
       <c r="E245" s="19" t="s">
@@ -7357,14 +7357,14 @@
         <v>73</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D257" s="3"/>
       <c r="F257" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -7372,14 +7372,14 @@
         <v>73</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D258" s="3"/>
       <c r="F258" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -7387,10 +7387,10 @@
         <v>73</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D259" s="3"/>
       <c r="F259" t="s">
@@ -7402,10 +7402,10 @@
         <v>73</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D260" s="3"/>
       <c r="F260" t="s">
@@ -7417,10 +7417,10 @@
         <v>73</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C261" s="3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D261" s="3"/>
       <c r="F261" t="s">
@@ -7432,10 +7432,10 @@
         <v>73</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C262" s="3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D262" s="3"/>
       <c r="F262" t="s">
@@ -7447,10 +7447,10 @@
         <v>73</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C263" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D263" s="3"/>
       <c r="F263" t="s">
@@ -7462,10 +7462,10 @@
         <v>73</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D264" s="3"/>
       <c r="F264" t="s">
@@ -7477,10 +7477,10 @@
         <v>73</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C265" s="3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D265" s="3"/>
       <c r="F265" t="s">
@@ -7492,10 +7492,10 @@
         <v>73</v>
       </c>
       <c r="B266" s="3" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C266" s="3" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D266" s="3"/>
       <c r="F266" t="s">
@@ -7507,14 +7507,14 @@
         <v>73</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C267" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D267" s="3"/>
       <c r="F267" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -7522,14 +7522,14 @@
         <v>73</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C268" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D268" s="3"/>
       <c r="F268" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
@@ -7537,14 +7537,14 @@
         <v>73</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C269" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D269" s="3"/>
       <c r="F269" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="270" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
@@ -7552,14 +7552,14 @@
         <v>73</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C270" s="3" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D270" s="3"/>
       <c r="F270" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="271" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
@@ -7567,10 +7567,10 @@
         <v>73</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D271" s="3"/>
       <c r="F271" t="s">
@@ -7582,14 +7582,14 @@
         <v>73</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C272" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D272" s="3"/>
       <c r="F272" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
@@ -7597,10 +7597,10 @@
         <v>73</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C273" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D273" s="3"/>
       <c r="F273" t="s">
@@ -7612,10 +7612,10 @@
         <v>73</v>
       </c>
       <c r="B274" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C274" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D274" s="3"/>
       <c r="F274" t="s">
@@ -7627,14 +7627,14 @@
         <v>73</v>
       </c>
       <c r="B275" s="3" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C275" s="3" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D275" s="3"/>
       <c r="F275" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -7642,14 +7642,14 @@
         <v>73</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C276" s="3" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D276" s="3"/>
       <c r="F276" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
@@ -7657,10 +7657,10 @@
         <v>73</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C277" s="3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D277" s="3"/>
       <c r="F277" t="s">
@@ -7672,10 +7672,10 @@
         <v>73</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C278" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D278" s="3"/>
       <c r="F278" t="s">
@@ -7687,14 +7687,14 @@
         <v>73</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C279" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D279" s="3"/>
       <c r="F279" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
@@ -7702,10 +7702,10 @@
         <v>73</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C280" s="3" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D280" s="3"/>
       <c r="F280" t="s">
@@ -7717,14 +7717,14 @@
         <v>73</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C281" s="3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D281" s="3"/>
       <c r="F281" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
@@ -7732,10 +7732,10 @@
         <v>73</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C282" s="3" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D282" s="3"/>
       <c r="F282" t="s">
@@ -7747,10 +7747,10 @@
         <v>73</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C283" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D283" s="3"/>
       <c r="F283" t="s">
@@ -7762,10 +7762,10 @@
         <v>73</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C284" s="3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D284" s="3"/>
       <c r="F284" t="s">
@@ -7777,10 +7777,10 @@
         <v>73</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C285" s="3" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D285" s="3"/>
       <c r="F285" t="s">
@@ -7792,10 +7792,10 @@
         <v>73</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C286" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D286" s="3"/>
       <c r="F286" t="s">
@@ -7807,10 +7807,10 @@
         <v>73</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C287" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D287" s="3"/>
       <c r="F287" t="s">
@@ -7822,14 +7822,14 @@
         <v>73</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C288" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D288" s="3"/>
       <c r="F288" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -7837,14 +7837,14 @@
         <v>73</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C289" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D289" s="3"/>
       <c r="F289" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -7852,14 +7852,14 @@
         <v>73</v>
       </c>
       <c r="B290" s="3" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C290" s="3" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D290" s="3"/>
       <c r="F290" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -7867,14 +7867,14 @@
         <v>73</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C291" s="3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D291" s="3"/>
       <c r="F291" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="292" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
@@ -7882,14 +7882,14 @@
         <v>73</v>
       </c>
       <c r="B292" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C292" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D292" s="3"/>
       <c r="F292" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="293" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
@@ -7897,14 +7897,14 @@
         <v>73</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C293" s="3" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D293" s="3"/>
       <c r="F293" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -7912,14 +7912,14 @@
         <v>73</v>
       </c>
       <c r="B294" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C294" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D294" s="3"/>
       <c r="F294" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -7927,14 +7927,14 @@
         <v>73</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C295" s="3" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D295" s="3"/>
       <c r="F295" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="296" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
@@ -7942,14 +7942,14 @@
         <v>73</v>
       </c>
       <c r="B296" s="3" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D296" s="3"/>
       <c r="F296" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -7957,14 +7957,14 @@
         <v>73</v>
       </c>
       <c r="B297" s="3" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C297" s="3" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D297" s="3"/>
       <c r="F297" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -7972,14 +7972,14 @@
         <v>73</v>
       </c>
       <c r="B298" s="3" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C298" s="3" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D298" s="3"/>
       <c r="F298" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="299" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
@@ -7987,14 +7987,14 @@
         <v>73</v>
       </c>
       <c r="B299" s="3" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C299" s="3" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D299" s="3"/>
       <c r="F299" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -8002,14 +8002,14 @@
         <v>73</v>
       </c>
       <c r="B300" s="3" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C300" s="3" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D300" s="3"/>
       <c r="F300" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
@@ -8017,10 +8017,10 @@
         <v>73</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C301" s="3" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D301" s="3"/>
       <c r="F301" t="s">
@@ -8032,10 +8032,10 @@
         <v>73</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C302" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D302" s="3"/>
       <c r="F302" t="s">
@@ -8047,14 +8047,14 @@
         <v>73</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C303" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D303" s="3"/>
       <c r="F303" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
@@ -8062,14 +8062,14 @@
         <v>73</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C304" s="3" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D304" s="3"/>
       <c r="F304" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
@@ -8077,14 +8077,14 @@
         <v>73</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C305" s="3" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D305" s="3"/>
       <c r="F305" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
@@ -8092,14 +8092,14 @@
         <v>73</v>
       </c>
       <c r="B306" s="3" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C306" s="3" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D306" s="3"/>
       <c r="F306" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
@@ -8107,14 +8107,14 @@
         <v>73</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C307" s="3" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D307" s="3"/>
       <c r="F307" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
@@ -8122,14 +8122,14 @@
         <v>73</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C308" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D308" s="3"/>
       <c r="F308" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
@@ -8137,14 +8137,14 @@
         <v>73</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C309" s="3" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D309" s="3"/>
       <c r="F309" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
@@ -8152,14 +8152,14 @@
         <v>73</v>
       </c>
       <c r="B310" s="3" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C310" s="3" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D310" s="3"/>
       <c r="F310" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="311" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
@@ -8167,14 +8167,14 @@
         <v>73</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C311" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D311" s="3"/>
       <c r="F311" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="312" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
@@ -8182,14 +8182,14 @@
         <v>73</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C312" s="3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D312" s="3"/>
       <c r="F312" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
@@ -8197,14 +8197,14 @@
         <v>73</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C313" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D313" s="3"/>
       <c r="F313" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
@@ -8212,14 +8212,14 @@
         <v>73</v>
       </c>
       <c r="B314" s="3" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C314" s="3" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D314" s="3"/>
       <c r="F314" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
@@ -8227,14 +8227,14 @@
         <v>73</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C315" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D315" s="3"/>
       <c r="F315" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
@@ -8242,14 +8242,14 @@
         <v>73</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C316" s="3" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D316" s="3"/>
       <c r="F316" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
@@ -8257,14 +8257,14 @@
         <v>73</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C317" s="3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D317" s="3"/>
       <c r="F317" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
@@ -8272,10 +8272,10 @@
         <v>73</v>
       </c>
       <c r="B318" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C318" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D318" s="3"/>
       <c r="F318" t="s">
@@ -8287,10 +8287,10 @@
         <v>73</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C319" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D319" s="3"/>
       <c r="F319" t="s">
@@ -8302,10 +8302,10 @@
         <v>73</v>
       </c>
       <c r="B320" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C320" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D320" s="3"/>
       <c r="F320" t="s">
@@ -8317,14 +8317,14 @@
         <v>73</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C321" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D321" s="3"/>
       <c r="F321" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
@@ -8332,14 +8332,14 @@
         <v>73</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C322" s="3" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D322" s="3"/>
       <c r="F322" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
@@ -8347,10 +8347,10 @@
         <v>73</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C323" s="3" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D323" s="3"/>
       <c r="F323" t="s">
@@ -8362,10 +8362,10 @@
         <v>73</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C324" s="3" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D324" s="3"/>
       <c r="F324" t="s">
@@ -8377,10 +8377,10 @@
         <v>73</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C325" s="3" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D325" s="3"/>
       <c r="F325" t="s">
@@ -8392,10 +8392,10 @@
         <v>73</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C326" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D326" s="3"/>
       <c r="F326" t="s">
@@ -8407,10 +8407,10 @@
         <v>73</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C327" s="3" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D327" s="3"/>
       <c r="F327" t="s">
@@ -8422,10 +8422,10 @@
         <v>73</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C328" s="3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D328" s="3"/>
       <c r="F328" t="s">
@@ -8437,14 +8437,14 @@
         <v>73</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C329" s="3" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D329" s="3"/>
       <c r="F329" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="330" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
@@ -8452,14 +8452,14 @@
         <v>73</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C330" s="3" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D330" s="3"/>
       <c r="F330" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
@@ -8467,14 +8467,14 @@
         <v>73</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C331" s="3" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D331" s="3"/>
       <c r="F331" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="332" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
@@ -8482,10 +8482,10 @@
         <v>73</v>
       </c>
       <c r="B332" s="3" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C332" s="3" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D332" s="3"/>
       <c r="F332" t="s">
@@ -8497,10 +8497,10 @@
         <v>73</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C333" s="3" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D333" s="3"/>
       <c r="F333" t="s">
@@ -8512,14 +8512,14 @@
         <v>73</v>
       </c>
       <c r="B334" s="3" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C334" s="3" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D334" s="3"/>
       <c r="F334" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
@@ -8527,10 +8527,10 @@
         <v>73</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C335" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D335" s="3"/>
       <c r="F335" t="s">
@@ -8542,10 +8542,10 @@
         <v>73</v>
       </c>
       <c r="B336" s="3" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C336" s="3" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D336" s="3"/>
       <c r="F336" t="s">
@@ -8557,14 +8557,14 @@
         <v>73</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C337" s="3" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D337" s="3"/>
       <c r="F337" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
@@ -8572,10 +8572,10 @@
         <v>73</v>
       </c>
       <c r="B338" s="3" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D338" s="3"/>
       <c r="F338" t="s">
@@ -8587,10 +8587,10 @@
         <v>73</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D339" s="3"/>
       <c r="F339" t="s">
@@ -8602,10 +8602,10 @@
         <v>73</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C340" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D340" s="3"/>
       <c r="F340" t="s">
@@ -8617,10 +8617,10 @@
         <v>73</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C341" s="3" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D341" s="3"/>
       <c r="F341" t="s">
@@ -8632,10 +8632,10 @@
         <v>73</v>
       </c>
       <c r="B342" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C342" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D342" s="3"/>
       <c r="F342" t="s">
@@ -8647,14 +8647,14 @@
         <v>73</v>
       </c>
       <c r="B343" s="3" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C343" s="3" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D343" s="3"/>
       <c r="F343" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
@@ -8662,10 +8662,10 @@
         <v>73</v>
       </c>
       <c r="B344" s="3" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C344" s="3" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D344" s="3"/>
       <c r="F344" t="s">
@@ -8677,10 +8677,10 @@
         <v>73</v>
       </c>
       <c r="B345" s="3" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C345" s="3" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D345" s="3"/>
       <c r="F345" t="s">
@@ -8692,14 +8692,14 @@
         <v>73</v>
       </c>
       <c r="B346" s="3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C346" s="3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D346" s="3"/>
       <c r="F346" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
@@ -8707,10 +8707,10 @@
         <v>73</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C347" s="3" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D347" s="3"/>
       <c r="F347" t="s">
@@ -8722,14 +8722,14 @@
         <v>73</v>
       </c>
       <c r="B348" s="3" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C348" s="3" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D348" s="3"/>
       <c r="F348" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
@@ -8737,14 +8737,14 @@
         <v>73</v>
       </c>
       <c r="B349" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C349" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D349" s="3"/>
       <c r="F349" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
@@ -8752,10 +8752,10 @@
         <v>73</v>
       </c>
       <c r="B350" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C350" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D350" s="3"/>
       <c r="F350" t="s">
@@ -8767,10 +8767,10 @@
         <v>73</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C351" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D351" s="3"/>
       <c r="F351" t="s">
@@ -8782,10 +8782,10 @@
         <v>73</v>
       </c>
       <c r="B352" s="3" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C352" s="3" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D352" s="3"/>
       <c r="F352" t="s">
@@ -8797,14 +8797,14 @@
         <v>73</v>
       </c>
       <c r="B353" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C353" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D353" s="3"/>
       <c r="F353" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="354" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
@@ -8812,10 +8812,10 @@
         <v>73</v>
       </c>
       <c r="B354" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C354" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D354" s="3"/>
       <c r="F354" t="s">
@@ -8827,10 +8827,10 @@
         <v>73</v>
       </c>
       <c r="B355" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C355" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D355" s="3"/>
       <c r="F355" t="s">
@@ -8842,10 +8842,10 @@
         <v>73</v>
       </c>
       <c r="B356" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C356" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D356" s="3"/>
       <c r="F356" t="s">
@@ -8857,10 +8857,10 @@
         <v>73</v>
       </c>
       <c r="B357" s="3" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C357" s="3" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D357" s="3"/>
       <c r="F357" t="s">
@@ -8872,10 +8872,10 @@
         <v>73</v>
       </c>
       <c r="B358" s="3" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C358" s="3" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D358" s="3"/>
       <c r="F358" t="s">
@@ -8887,14 +8887,14 @@
         <v>73</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C359" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D359" s="3"/>
       <c r="F359" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.25">
@@ -8902,14 +8902,14 @@
         <v>73</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C360" s="3" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D360" s="3"/>
       <c r="F360" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.25">
@@ -8917,14 +8917,14 @@
         <v>73</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C361" s="3" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D361" s="3"/>
       <c r="F361" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.25">
@@ -8932,14 +8932,14 @@
         <v>73</v>
       </c>
       <c r="B362" s="3" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C362" s="3" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D362" s="3"/>
       <c r="F362" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.25">
@@ -8947,10 +8947,10 @@
         <v>73</v>
       </c>
       <c r="B363" s="3" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C363" s="3" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D363" s="3"/>
       <c r="F363" t="s">
@@ -8962,14 +8962,14 @@
         <v>73</v>
       </c>
       <c r="B364" s="3" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C364" s="3" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D364" s="3"/>
       <c r="F364" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.25">
@@ -8977,10 +8977,10 @@
         <v>73</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C365" s="3" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D365" s="3"/>
       <c r="F365" t="s">
@@ -8992,10 +8992,10 @@
         <v>73</v>
       </c>
       <c r="B366" s="3" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C366" s="3" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D366" s="3"/>
       <c r="F366" t="s">
@@ -9007,10 +9007,10 @@
         <v>73</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C367" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D367" s="3"/>
       <c r="F367" t="s">
@@ -9022,14 +9022,14 @@
         <v>73</v>
       </c>
       <c r="B368" s="3" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C368" s="3" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D368" s="3"/>
       <c r="F368" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.25">
@@ -9037,10 +9037,10 @@
         <v>73</v>
       </c>
       <c r="B369" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C369" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D369" s="3"/>
       <c r="F369" t="s">
@@ -9052,10 +9052,10 @@
         <v>73</v>
       </c>
       <c r="B370" s="3" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C370" s="3" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D370" s="3"/>
       <c r="F370" t="s">
@@ -9067,14 +9067,14 @@
         <v>73</v>
       </c>
       <c r="B371" s="3" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C371" s="3" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D371" s="3"/>
       <c r="F371" t="s">
-        <v>351</v>
+        <v>574</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.25">
@@ -9082,14 +9082,14 @@
         <v>73</v>
       </c>
       <c r="B372" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C372" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D372" s="3"/>
       <c r="F372" t="s">
-        <v>351</v>
+        <v>574</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.25">
@@ -9097,14 +9097,14 @@
         <v>73</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>542</v>
+        <v>575</v>
       </c>
       <c r="C373" s="3" t="s">
-        <v>542</v>
+        <v>575</v>
       </c>
       <c r="D373" s="3"/>
       <c r="F373" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="374" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
@@ -9112,14 +9112,14 @@
         <v>73</v>
       </c>
       <c r="B374" s="3" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C374" s="3" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="D374" s="3"/>
       <c r="F374" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
@@ -9127,14 +9127,14 @@
         <v>73</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C375" s="3" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="D375" s="3"/>
       <c r="F375" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.25">
@@ -9142,10 +9142,10 @@
         <v>73</v>
       </c>
       <c r="B376" s="3" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C376" s="3" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D376" s="3"/>
       <c r="F376" t="s">
@@ -9157,10 +9157,10 @@
         <v>73</v>
       </c>
       <c r="B377" s="3" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C377" s="3" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="D377" s="3"/>
       <c r="F377" t="s">
@@ -9172,14 +9172,14 @@
         <v>73</v>
       </c>
       <c r="B378" s="3" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C378" s="3" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="D378" s="3"/>
       <c r="F378" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
@@ -9187,14 +9187,14 @@
         <v>73</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C379" s="3" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="D379" s="3"/>
       <c r="F379" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.25">
@@ -9202,14 +9202,14 @@
         <v>73</v>
       </c>
       <c r="B380" s="3" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C380" s="3" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D380" s="3"/>
       <c r="F380" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.25">
@@ -9217,14 +9217,14 @@
         <v>73</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C381" s="3" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="D381" s="3"/>
       <c r="F381" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.25">
@@ -9232,10 +9232,10 @@
         <v>73</v>
       </c>
       <c r="B382" s="3" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C382" s="3" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="D382" s="3"/>
       <c r="F382" t="s">
@@ -9247,14 +9247,14 @@
         <v>73</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C383" s="3" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="D383" s="3"/>
       <c r="F383" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="384" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
@@ -9262,14 +9262,14 @@
         <v>73</v>
       </c>
       <c r="B384" s="3" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C384" s="3" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="D384" s="3"/>
       <c r="F384" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.25">
@@ -9277,10 +9277,10 @@
         <v>73</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C385" s="3" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D385" s="3"/>
       <c r="F385" t="s">
@@ -9292,10 +9292,10 @@
         <v>73</v>
       </c>
       <c r="B386" s="3" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C386" s="3" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="D386" s="3"/>
       <c r="F386" t="s">
@@ -9307,10 +9307,10 @@
         <v>73</v>
       </c>
       <c r="B387" s="3" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C387" s="3" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="D387" s="3"/>
       <c r="F387" t="s">
@@ -9322,10 +9322,10 @@
         <v>73</v>
       </c>
       <c r="B388" s="3" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C388" s="3" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="D388" s="3"/>
       <c r="F388" t="s">
@@ -9337,10 +9337,10 @@
         <v>73</v>
       </c>
       <c r="B389" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C389" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="D389" s="3"/>
       <c r="F389" t="s">
@@ -9352,10 +9352,10 @@
         <v>73</v>
       </c>
       <c r="B390" s="3" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C390" s="3" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="D390" s="3"/>
       <c r="F390" t="s">
@@ -9367,10 +9367,10 @@
         <v>73</v>
       </c>
       <c r="B391" s="3" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C391" s="3" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="D391" s="3"/>
       <c r="F391" t="s">
@@ -9382,10 +9382,10 @@
         <v>73</v>
       </c>
       <c r="B392" s="3" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C392" s="3" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="D392" s="3"/>
       <c r="F392" t="s">
@@ -9397,10 +9397,10 @@
         <v>73</v>
       </c>
       <c r="B393" s="3" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C393" s="3" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="D393" s="3"/>
       <c r="F393" t="s">
@@ -9412,10 +9412,10 @@
         <v>73</v>
       </c>
       <c r="B394" s="3" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C394" s="3" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D394" s="3"/>
       <c r="F394" t="s">
@@ -9427,10 +9427,10 @@
         <v>73</v>
       </c>
       <c r="B395" s="3" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C395" s="3" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="D395" s="3"/>
       <c r="F395" t="s">
@@ -9442,14 +9442,14 @@
         <v>73</v>
       </c>
       <c r="B396" s="3" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C396" s="3" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="D396" s="3"/>
       <c r="F396" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.25">
@@ -9457,14 +9457,14 @@
         <v>73</v>
       </c>
       <c r="B397" s="3" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C397" s="3" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D397" s="3"/>
       <c r="F397" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.25">
@@ -9472,14 +9472,14 @@
         <v>73</v>
       </c>
       <c r="B398" s="3" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C398" s="3" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="D398" s="3"/>
       <c r="F398" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.25">
@@ -9487,14 +9487,14 @@
         <v>73</v>
       </c>
       <c r="B399" s="3" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="C399" s="3" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="D399" s="3"/>
       <c r="F399" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.25">
@@ -9502,14 +9502,14 @@
         <v>73</v>
       </c>
       <c r="B400" s="3" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C400" s="3" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="D400" s="3"/>
       <c r="F400" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="401" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
@@ -9517,14 +9517,14 @@
         <v>73</v>
       </c>
       <c r="B401" s="3" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C401" s="3" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="D401" s="3"/>
       <c r="F401" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.25">
@@ -9532,14 +9532,14 @@
         <v>73</v>
       </c>
       <c r="B402" s="3" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C402" s="3" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="D402" s="3"/>
       <c r="F402" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.25">
@@ -9547,14 +9547,14 @@
         <v>73</v>
       </c>
       <c r="B403" s="3" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C403" s="3" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="D403" s="3"/>
       <c r="F403" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.25">
@@ -9562,14 +9562,14 @@
         <v>73</v>
       </c>
       <c r="B404" s="3" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C404" s="3" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="D404" s="3"/>
       <c r="F404" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.25">
@@ -9577,14 +9577,14 @@
         <v>73</v>
       </c>
       <c r="B405" s="3" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C405" s="3" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="D405" s="3"/>
       <c r="F405" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.25">
@@ -9592,14 +9592,14 @@
         <v>73</v>
       </c>
       <c r="B406" s="3" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C406" s="3" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="D406" s="3"/>
       <c r="F406" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.25">
@@ -10484,7 +10484,7 @@
       </c>
       <c r="D465" s="3"/>
       <c r="F465" t="s">
-        <v>351</v>
+        <v>574</v>
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.25">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="D466" s="3"/>
       <c r="F466" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.25">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="D467" s="3"/>
       <c r="F467" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.25">
@@ -10529,7 +10529,7 @@
       </c>
       <c r="D468" s="3"/>
       <c r="F468" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.25">
@@ -10544,7 +10544,7 @@
       </c>
       <c r="D469" s="3"/>
       <c r="F469" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.25">
@@ -10559,7 +10559,7 @@
       </c>
       <c r="D470" s="3"/>
       <c r="F470" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.25">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="D471" s="3"/>
       <c r="F471" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.25">
@@ -10589,7 +10589,7 @@
       </c>
       <c r="D472" s="3"/>
       <c r="F472" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.25">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="D473" s="3"/>
       <c r="F473" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.25">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="D474" s="3"/>
       <c r="F474" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.25">
@@ -10634,7 +10634,7 @@
       </c>
       <c r="D475" s="3"/>
       <c r="F475" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.25">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="D476" s="3"/>
       <c r="F476" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.25">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="D477" s="3"/>
       <c r="F477" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.25">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="D478" s="3"/>
       <c r="F478" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.25">
@@ -10694,7 +10694,7 @@
       </c>
       <c r="D479" s="3"/>
       <c r="F479" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.25">
@@ -10709,7 +10709,7 @@
       </c>
       <c r="D480" s="3"/>
       <c r="F480" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.25">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="D481" s="3"/>
       <c r="F481" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.25">
@@ -10739,7 +10739,7 @@
       </c>
       <c r="D482" s="3"/>
       <c r="F482" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.25">
@@ -10754,7 +10754,7 @@
       </c>
       <c r="D483" s="3"/>
       <c r="F483" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.25">
@@ -10769,7 +10769,7 @@
       </c>
       <c r="D484" s="3"/>
       <c r="F484" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.25">
@@ -10784,7 +10784,7 @@
       </c>
       <c r="D485" s="3"/>
       <c r="F485" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.25">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="D486" s="3"/>
       <c r="F486" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.25">
@@ -10814,7 +10814,7 @@
       </c>
       <c r="D487" s="3"/>
       <c r="F487" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.25">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="D488" s="3"/>
       <c r="F488" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.25">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="D489" s="3"/>
       <c r="F489" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.25">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="D490" s="3"/>
       <c r="F490" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.25">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="D491" s="3"/>
       <c r="F491" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.25">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="D492" s="3"/>
       <c r="F492" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.25">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="D493" s="3"/>
       <c r="F493" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.25">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="D494" s="3"/>
       <c r="F494" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.25">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="D495" s="3"/>
       <c r="F495" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.25">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="D496" s="3"/>
       <c r="F496" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.25">
@@ -10964,7 +10964,7 @@
       </c>
       <c r="D497" s="3"/>
       <c r="F497" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.25">
@@ -10979,7 +10979,7 @@
       </c>
       <c r="D498" s="3"/>
       <c r="F498" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.25">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="D499" s="3"/>
       <c r="F499" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="500" spans="1:6" x14ac:dyDescent="0.25">
@@ -11009,7 +11009,7 @@
       </c>
       <c r="D500" s="3"/>
       <c r="F500" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="501" spans="1:6" x14ac:dyDescent="0.25">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="D501" s="3"/>
       <c r="F501" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.25">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="D502" s="3"/>
       <c r="F502" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.25">
@@ -11054,7 +11054,7 @@
       </c>
       <c r="D503" s="3"/>
       <c r="F503" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="504" spans="1:6" x14ac:dyDescent="0.25">
@@ -11069,7 +11069,7 @@
       </c>
       <c r="D504" s="3"/>
       <c r="F504" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.25">
@@ -11084,7 +11084,7 @@
       </c>
       <c r="D505" s="3"/>
       <c r="F505" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="506" spans="1:6" x14ac:dyDescent="0.25">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="D506" s="3"/>
       <c r="F506" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="507" spans="1:6" x14ac:dyDescent="0.25">
@@ -11114,7 +11114,7 @@
       </c>
       <c r="D507" s="3"/>
       <c r="F507" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="508" spans="1:6" x14ac:dyDescent="0.25">
@@ -11129,7 +11129,7 @@
       </c>
       <c r="D508" s="3"/>
       <c r="F508" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="509" spans="1:6" x14ac:dyDescent="0.25">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="D509" s="3"/>
       <c r="F509" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="510" spans="1:6" x14ac:dyDescent="0.25">
@@ -11159,7 +11159,7 @@
       </c>
       <c r="D510" s="3"/>
       <c r="F510" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="511" spans="1:6" x14ac:dyDescent="0.25">
@@ -11174,7 +11174,7 @@
       </c>
       <c r="D511" s="3"/>
       <c r="F511" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="512" spans="1:6" x14ac:dyDescent="0.25">
@@ -11189,7 +11189,7 @@
       </c>
       <c r="D512" s="3"/>
       <c r="F512" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="513" spans="1:6" x14ac:dyDescent="0.25">
@@ -11204,7 +11204,7 @@
       </c>
       <c r="D513" s="3"/>
       <c r="F513" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="514" spans="1:6" x14ac:dyDescent="0.25">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="D514" s="3"/>
       <c r="F514" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="515" spans="1:6" x14ac:dyDescent="0.25">
@@ -11234,7 +11234,7 @@
       </c>
       <c r="D515" s="3"/>
       <c r="F515" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="516" spans="1:6" x14ac:dyDescent="0.25">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="D516" s="3"/>
       <c r="F516" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="517" spans="1:6" x14ac:dyDescent="0.25">
@@ -11264,7 +11264,7 @@
       </c>
       <c r="D517" s="3"/>
       <c r="F517" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="518" spans="1:6" x14ac:dyDescent="0.25">
@@ -11279,7 +11279,7 @@
       </c>
       <c r="D518" s="3"/>
       <c r="F518" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="519" spans="1:6" x14ac:dyDescent="0.25">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="D519" s="3"/>
       <c r="F519" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="520" spans="1:6" x14ac:dyDescent="0.25">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="D520" s="3"/>
       <c r="F520" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="521" spans="1:6" x14ac:dyDescent="0.25">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="D521" s="3"/>
       <c r="F521" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="522" spans="1:6" x14ac:dyDescent="0.25">
@@ -11339,7 +11339,7 @@
       </c>
       <c r="D522" s="3"/>
       <c r="F522" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="523" spans="1:6" x14ac:dyDescent="0.25">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="D523" s="3"/>
       <c r="F523" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="524" spans="1:6" x14ac:dyDescent="0.25">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="D524" s="3"/>
       <c r="F524" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="525" spans="1:6" x14ac:dyDescent="0.25">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="D525" s="3"/>
       <c r="F525" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="526" spans="1:6" x14ac:dyDescent="0.25">
@@ -11399,7 +11399,7 @@
       </c>
       <c r="D526" s="3"/>
       <c r="F526" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="527" spans="1:6" x14ac:dyDescent="0.25">
@@ -11414,7 +11414,7 @@
       </c>
       <c r="D527" s="3"/>
       <c r="F527" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="528" spans="1:6" x14ac:dyDescent="0.25">
@@ -11429,7 +11429,7 @@
       </c>
       <c r="D528" s="3"/>
       <c r="F528" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="529" spans="1:7" x14ac:dyDescent="0.25">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="D529" s="3"/>
       <c r="F529" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="530" spans="1:7" x14ac:dyDescent="0.25">
@@ -11459,7 +11459,7 @@
       </c>
       <c r="D530" s="3"/>
       <c r="F530" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="531" spans="1:7" x14ac:dyDescent="0.25">
@@ -11474,7 +11474,7 @@
       </c>
       <c r="D531" s="3"/>
       <c r="F531" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="532" spans="1:7" x14ac:dyDescent="0.25">
@@ -11489,7 +11489,7 @@
       </c>
       <c r="D532" s="3"/>
       <c r="F532" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="533" spans="1:7" x14ac:dyDescent="0.25">
@@ -11504,7 +11504,7 @@
       </c>
       <c r="D533" s="3"/>
       <c r="F533" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="534" spans="1:7" x14ac:dyDescent="0.25">
@@ -11519,7 +11519,7 @@
       </c>
       <c r="D534" s="3"/>
       <c r="F534" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="535" spans="1:7" x14ac:dyDescent="0.25">
@@ -11534,7 +11534,7 @@
       </c>
       <c r="D535" s="3"/>
       <c r="F535" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="536" spans="1:7" x14ac:dyDescent="0.25">
@@ -11549,7 +11549,7 @@
       </c>
       <c r="D536" s="3"/>
       <c r="F536" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="537" spans="1:7" x14ac:dyDescent="0.25">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="D537" s="3"/>
       <c r="F537" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="538" spans="1:7" x14ac:dyDescent="0.25">
@@ -11579,7 +11579,7 @@
       </c>
       <c r="D538" s="3"/>
       <c r="F538" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="539" spans="1:7" x14ac:dyDescent="0.25">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="D539" s="3"/>
       <c r="F539" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="540" spans="1:7" x14ac:dyDescent="0.25">
@@ -11609,7 +11609,7 @@
       </c>
       <c r="D540" s="3"/>
       <c r="F540" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="541" spans="1:7" x14ac:dyDescent="0.25">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="D542" s="6"/>
       <c r="G542" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="543" spans="1:7" x14ac:dyDescent="0.25">
@@ -11644,7 +11644,7 @@
       </c>
       <c r="D543" s="6"/>
       <c r="G543" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="544" spans="1:7" x14ac:dyDescent="0.25">
@@ -11659,7 +11659,7 @@
       </c>
       <c r="D544" s="6"/>
       <c r="G544" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="545" spans="1:7" x14ac:dyDescent="0.25">
@@ -11674,7 +11674,7 @@
       </c>
       <c r="D545" s="6"/>
       <c r="G545" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="546" spans="1:7" x14ac:dyDescent="0.25">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="D546" s="6"/>
       <c r="G546" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="547" spans="1:7" x14ac:dyDescent="0.25">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="D547" s="6"/>
       <c r="G547" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="548" spans="1:7" x14ac:dyDescent="0.25">
@@ -11719,7 +11719,7 @@
       </c>
       <c r="D548" s="6"/>
       <c r="G548" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="549" spans="1:7" x14ac:dyDescent="0.25">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="D549" s="6"/>
       <c r="G549" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="550" spans="1:7" x14ac:dyDescent="0.25">
@@ -11749,7 +11749,7 @@
       </c>
       <c r="D550" s="6"/>
       <c r="G550" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="551" spans="1:7" x14ac:dyDescent="0.25">
@@ -11764,7 +11764,7 @@
       </c>
       <c r="D551" s="6"/>
       <c r="G551" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="552" spans="1:7" x14ac:dyDescent="0.25">
@@ -11779,7 +11779,7 @@
       </c>
       <c r="D552" s="6"/>
       <c r="G552" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="553" spans="1:7" x14ac:dyDescent="0.25">
@@ -11794,7 +11794,7 @@
       </c>
       <c r="D553" s="6"/>
       <c r="G553" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="554" spans="1:7" x14ac:dyDescent="0.25">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="D554" s="6"/>
       <c r="G554" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="555" spans="1:7" x14ac:dyDescent="0.25">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="D555" s="6"/>
       <c r="G555" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="556" spans="1:7" x14ac:dyDescent="0.25">
@@ -11839,7 +11839,7 @@
       </c>
       <c r="D556" s="6"/>
       <c r="G556" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="557" spans="1:7" x14ac:dyDescent="0.25">
@@ -11854,7 +11854,7 @@
       </c>
       <c r="D557" s="6"/>
       <c r="G557" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="558" spans="1:7" x14ac:dyDescent="0.25">
@@ -11869,7 +11869,7 @@
       </c>
       <c r="D558" s="6"/>
       <c r="G558" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="559" spans="1:7" x14ac:dyDescent="0.25">
@@ -11884,7 +11884,7 @@
       </c>
       <c r="D559" s="6"/>
       <c r="G559" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="560" spans="1:7" x14ac:dyDescent="0.25">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="D560" s="6"/>
       <c r="G560" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="561" spans="1:7" x14ac:dyDescent="0.25">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="D561" s="6"/>
       <c r="G561" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="562" spans="1:7" x14ac:dyDescent="0.25">
@@ -11929,7 +11929,7 @@
       </c>
       <c r="D562" s="6"/>
       <c r="G562" t="s">
-        <v>542</v>
+        <v>575</v>
       </c>
     </row>
     <row r="563" spans="1:7" x14ac:dyDescent="0.25">
@@ -11944,7 +11944,7 @@
       </c>
       <c r="D563" s="6"/>
       <c r="G563" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="564" spans="1:7" x14ac:dyDescent="0.25">
@@ -11959,7 +11959,7 @@
       </c>
       <c r="D564" s="6"/>
       <c r="G564" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="565" spans="1:7" x14ac:dyDescent="0.25">
@@ -11974,7 +11974,7 @@
       </c>
       <c r="D565" s="6"/>
       <c r="G565" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="566" spans="1:7" x14ac:dyDescent="0.25">
@@ -11989,7 +11989,7 @@
       </c>
       <c r="D566" s="6"/>
       <c r="G566" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="567" spans="1:7" x14ac:dyDescent="0.25">
@@ -12004,7 +12004,7 @@
       </c>
       <c r="D567" s="6"/>
       <c r="G567" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="568" spans="1:7" x14ac:dyDescent="0.25">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="D568" s="6"/>
       <c r="G568" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="569" spans="1:7" x14ac:dyDescent="0.25">
@@ -12034,7 +12034,7 @@
       </c>
       <c r="D569" s="6"/>
       <c r="G569" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="570" spans="1:7" x14ac:dyDescent="0.25">
@@ -12049,7 +12049,7 @@
       </c>
       <c r="D570" s="6"/>
       <c r="G570" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="571" spans="1:7" x14ac:dyDescent="0.25">
@@ -12064,7 +12064,7 @@
       </c>
       <c r="D571" s="6"/>
       <c r="G571" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="572" spans="1:7" x14ac:dyDescent="0.25">
@@ -12079,7 +12079,7 @@
       </c>
       <c r="D572" s="6"/>
       <c r="G572" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="573" spans="1:7" x14ac:dyDescent="0.25">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="D573" s="6"/>
       <c r="G573" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="574" spans="1:7" x14ac:dyDescent="0.25">
@@ -12109,7 +12109,7 @@
       </c>
       <c r="D574" s="6"/>
       <c r="G574" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="575" spans="1:7" x14ac:dyDescent="0.25">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="D575" s="6"/>
       <c r="G575" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="576" spans="1:7" x14ac:dyDescent="0.25">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="D576" s="6"/>
       <c r="G576" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="577" spans="1:7" x14ac:dyDescent="0.25">
@@ -12154,7 +12154,7 @@
       </c>
       <c r="D577" s="6"/>
       <c r="G577" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="578" spans="1:7" x14ac:dyDescent="0.25">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="D578" s="6"/>
       <c r="G578" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="579" spans="1:7" x14ac:dyDescent="0.25">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="D579" s="6"/>
       <c r="G579" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="580" spans="1:7" x14ac:dyDescent="0.25">
@@ -12199,7 +12199,7 @@
       </c>
       <c r="D580" s="6"/>
       <c r="G580" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="581" spans="1:7" x14ac:dyDescent="0.25">
@@ -12214,7 +12214,7 @@
       </c>
       <c r="D581" s="6"/>
       <c r="G581" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="582" spans="1:7" x14ac:dyDescent="0.25">
@@ -12229,7 +12229,7 @@
       </c>
       <c r="D582" s="6"/>
       <c r="G582" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="583" spans="1:7" x14ac:dyDescent="0.25">
@@ -12244,7 +12244,7 @@
       </c>
       <c r="D583" s="6"/>
       <c r="G583" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="584" spans="1:7" x14ac:dyDescent="0.25">
@@ -12259,7 +12259,7 @@
       </c>
       <c r="D584" s="6"/>
       <c r="G584" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="585" spans="1:7" x14ac:dyDescent="0.25">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="D585" s="6"/>
       <c r="G585" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="586" spans="1:7" x14ac:dyDescent="0.25">
@@ -12289,7 +12289,7 @@
       </c>
       <c r="D586" s="6"/>
       <c r="G586" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="587" spans="1:7" x14ac:dyDescent="0.25">
@@ -12304,7 +12304,7 @@
       </c>
       <c r="D587" s="6"/>
       <c r="G587" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="588" spans="1:7" x14ac:dyDescent="0.25">
@@ -12319,7 +12319,7 @@
       </c>
       <c r="D588" s="6"/>
       <c r="G588" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="589" spans="1:7" x14ac:dyDescent="0.25">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="D589" s="6"/>
       <c r="G589" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="590" spans="1:7" x14ac:dyDescent="0.25">
@@ -12349,7 +12349,7 @@
       </c>
       <c r="D590" s="6"/>
       <c r="G590" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="591" spans="1:7" x14ac:dyDescent="0.25">
@@ -12364,7 +12364,7 @@
       </c>
       <c r="D591" s="6"/>
       <c r="G591" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="592" spans="1:7" x14ac:dyDescent="0.25">
@@ -12379,7 +12379,7 @@
       </c>
       <c r="D592" s="6"/>
       <c r="G592" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="593" spans="1:7" x14ac:dyDescent="0.25">
@@ -12394,7 +12394,7 @@
       </c>
       <c r="D593" s="6"/>
       <c r="G593" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="594" spans="1:7" x14ac:dyDescent="0.25">
@@ -12409,7 +12409,7 @@
       </c>
       <c r="D594" s="6"/>
       <c r="G594" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="595" spans="1:7" x14ac:dyDescent="0.25">
@@ -12424,7 +12424,7 @@
       </c>
       <c r="D595" s="6"/>
       <c r="G595" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="596" spans="1:7" x14ac:dyDescent="0.25">
@@ -12439,7 +12439,7 @@
       </c>
       <c r="D596" s="6"/>
       <c r="G596" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="597" spans="1:7" x14ac:dyDescent="0.25">
@@ -12454,7 +12454,7 @@
       </c>
       <c r="D597" s="6"/>
       <c r="G597" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="598" spans="1:7" x14ac:dyDescent="0.25">
@@ -12469,7 +12469,7 @@
       </c>
       <c r="D598" s="6"/>
       <c r="G598" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="599" spans="1:7" x14ac:dyDescent="0.25">
@@ -12484,7 +12484,7 @@
       </c>
       <c r="D599" s="6"/>
       <c r="G599" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="600" spans="1:7" x14ac:dyDescent="0.25">
@@ -12499,7 +12499,7 @@
       </c>
       <c r="D600" s="6"/>
       <c r="G600" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="601" spans="1:7" x14ac:dyDescent="0.25">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="D601" s="6"/>
       <c r="G601" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="602" spans="1:7" x14ac:dyDescent="0.25">
@@ -12529,7 +12529,7 @@
       </c>
       <c r="D602" s="6"/>
       <c r="G602" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="603" spans="1:7" x14ac:dyDescent="0.25">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="D603" s="6"/>
       <c r="G603" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="604" spans="1:7" x14ac:dyDescent="0.25">
@@ -12559,7 +12559,7 @@
       </c>
       <c r="D604" s="6"/>
       <c r="G604" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="605" spans="1:7" x14ac:dyDescent="0.25">
@@ -12574,7 +12574,7 @@
       </c>
       <c r="D605" s="6"/>
       <c r="G605" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="606" spans="1:7" x14ac:dyDescent="0.25">
@@ -12589,7 +12589,7 @@
       </c>
       <c r="D606" s="6"/>
       <c r="G606" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="607" spans="1:7" x14ac:dyDescent="0.25">
@@ -12604,7 +12604,7 @@
       </c>
       <c r="D607" s="6"/>
       <c r="G607" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="608" spans="1:7" x14ac:dyDescent="0.25">
@@ -12619,7 +12619,7 @@
       </c>
       <c r="D608" s="6"/>
       <c r="G608" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="609" spans="1:7" x14ac:dyDescent="0.25">
@@ -12634,7 +12634,7 @@
       </c>
       <c r="D609" s="6"/>
       <c r="G609" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="610" spans="1:7" x14ac:dyDescent="0.25">
@@ -12649,7 +12649,7 @@
       </c>
       <c r="D610" s="6"/>
       <c r="G610" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="611" spans="1:7" x14ac:dyDescent="0.25">
@@ -12664,7 +12664,7 @@
       </c>
       <c r="D611" s="6"/>
       <c r="G611" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="612" spans="1:7" x14ac:dyDescent="0.25">
@@ -12679,7 +12679,7 @@
       </c>
       <c r="D612" s="6"/>
       <c r="G612" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="613" spans="1:7" x14ac:dyDescent="0.25">
@@ -12694,7 +12694,7 @@
       </c>
       <c r="D613" s="6"/>
       <c r="G613" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="614" spans="1:7" x14ac:dyDescent="0.25">
@@ -12709,7 +12709,7 @@
       </c>
       <c r="D614" s="6"/>
       <c r="G614" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="615" spans="1:7" x14ac:dyDescent="0.25">
@@ -12724,7 +12724,7 @@
       </c>
       <c r="D615" s="6"/>
       <c r="G615" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="616" spans="1:7" x14ac:dyDescent="0.25">
@@ -12739,7 +12739,7 @@
       </c>
       <c r="D616" s="6"/>
       <c r="G616" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="617" spans="1:7" x14ac:dyDescent="0.25">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="D617" s="6"/>
       <c r="G617" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="618" spans="1:7" x14ac:dyDescent="0.25">
@@ -12769,7 +12769,7 @@
       </c>
       <c r="D618" s="6"/>
       <c r="G618" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="619" spans="1:7" x14ac:dyDescent="0.25">
@@ -12784,7 +12784,7 @@
       </c>
       <c r="D619" s="6"/>
       <c r="G619" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="620" spans="1:7" x14ac:dyDescent="0.25">
@@ -12799,7 +12799,7 @@
       </c>
       <c r="D620" s="6"/>
       <c r="G620" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="621" spans="1:7" x14ac:dyDescent="0.25">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="D621" s="6"/>
       <c r="G621" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="622" spans="1:7" x14ac:dyDescent="0.25">
@@ -12829,7 +12829,7 @@
       </c>
       <c r="D622" s="6"/>
       <c r="G622" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="623" spans="1:7" x14ac:dyDescent="0.25">
@@ -12844,7 +12844,7 @@
       </c>
       <c r="D623" s="6"/>
       <c r="G623" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="624" spans="1:7" x14ac:dyDescent="0.25">
@@ -12859,7 +12859,7 @@
       </c>
       <c r="D624" s="6"/>
       <c r="G624" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="625" spans="1:7" x14ac:dyDescent="0.25">
@@ -12874,7 +12874,7 @@
       </c>
       <c r="D625" s="6"/>
       <c r="G625" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="626" spans="1:7" x14ac:dyDescent="0.25">
@@ -12889,7 +12889,7 @@
       </c>
       <c r="D626" s="6"/>
       <c r="G626" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="627" spans="1:7" x14ac:dyDescent="0.25">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="D627" s="6"/>
       <c r="G627" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="628" spans="1:7" x14ac:dyDescent="0.25">
@@ -12919,7 +12919,7 @@
       </c>
       <c r="D628" s="6"/>
       <c r="G628" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="629" spans="1:7" x14ac:dyDescent="0.25">
@@ -12934,7 +12934,7 @@
       </c>
       <c r="D629" s="6"/>
       <c r="G629" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="630" spans="1:7" x14ac:dyDescent="0.25">
@@ -12949,7 +12949,7 @@
       </c>
       <c r="D630" s="6"/>
       <c r="G630" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="631" spans="1:7" x14ac:dyDescent="0.25">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="D631" s="6"/>
       <c r="G631" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="632" spans="1:7" x14ac:dyDescent="0.25">
@@ -12979,7 +12979,7 @@
       </c>
       <c r="D632" s="6"/>
       <c r="G632" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="633" spans="1:7" x14ac:dyDescent="0.25">
@@ -12994,7 +12994,7 @@
       </c>
       <c r="D633" s="6"/>
       <c r="G633" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="634" spans="1:7" x14ac:dyDescent="0.25">
@@ -13009,7 +13009,7 @@
       </c>
       <c r="D634" s="6"/>
       <c r="G634" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="635" spans="1:7" x14ac:dyDescent="0.25">
@@ -13024,7 +13024,7 @@
       </c>
       <c r="D635" s="6"/>
       <c r="G635" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="636" spans="1:7" x14ac:dyDescent="0.25">
@@ -13039,7 +13039,7 @@
       </c>
       <c r="D636" s="6"/>
       <c r="G636" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="637" spans="1:7" x14ac:dyDescent="0.25">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="D637" s="6"/>
       <c r="G637" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="638" spans="1:7" x14ac:dyDescent="0.25">
@@ -13069,7 +13069,7 @@
       </c>
       <c r="D638" s="6"/>
       <c r="G638" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="639" spans="1:7" x14ac:dyDescent="0.25">
@@ -13084,7 +13084,7 @@
       </c>
       <c r="D639" s="6"/>
       <c r="G639" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="640" spans="1:7" x14ac:dyDescent="0.25">
@@ -13099,7 +13099,7 @@
       </c>
       <c r="D640" s="6"/>
       <c r="G640" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="641" spans="1:7" x14ac:dyDescent="0.25">
@@ -13113,7 +13113,7 @@
         <v>400</v>
       </c>
       <c r="G641" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="642" spans="1:7" x14ac:dyDescent="0.25">
@@ -13127,7 +13127,7 @@
         <v>401</v>
       </c>
       <c r="G642" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="643" spans="1:7" x14ac:dyDescent="0.25">
@@ -13141,7 +13141,7 @@
         <v>402</v>
       </c>
       <c r="G643" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="644" spans="1:7" x14ac:dyDescent="0.25">
@@ -13155,7 +13155,7 @@
         <v>403</v>
       </c>
       <c r="G644" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="645" spans="1:7" x14ac:dyDescent="0.25">
@@ -13169,7 +13169,7 @@
         <v>404</v>
       </c>
       <c r="G645" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="646" spans="1:7" x14ac:dyDescent="0.25">
@@ -13183,7 +13183,7 @@
         <v>405</v>
       </c>
       <c r="G646" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="647" spans="1:7" x14ac:dyDescent="0.25">
@@ -13197,7 +13197,7 @@
         <v>406</v>
       </c>
       <c r="G647" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="648" spans="1:7" x14ac:dyDescent="0.25">
@@ -13211,7 +13211,7 @@
         <v>407</v>
       </c>
       <c r="G648" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="649" spans="1:7" x14ac:dyDescent="0.25">
@@ -13225,7 +13225,7 @@
         <v>408</v>
       </c>
       <c r="G649" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="650" spans="1:7" x14ac:dyDescent="0.25">
@@ -13239,7 +13239,7 @@
         <v>409</v>
       </c>
       <c r="G650" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="651" spans="1:7" x14ac:dyDescent="0.25">
@@ -13253,7 +13253,7 @@
         <v>410</v>
       </c>
       <c r="G651" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="652" spans="1:7" x14ac:dyDescent="0.25">
@@ -13267,7 +13267,7 @@
         <v>411</v>
       </c>
       <c r="G652" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="653" spans="1:7" x14ac:dyDescent="0.25">
@@ -13281,7 +13281,7 @@
         <v>412</v>
       </c>
       <c r="G653" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="654" spans="1:7" x14ac:dyDescent="0.25">
@@ -13295,7 +13295,7 @@
         <v>413</v>
       </c>
       <c r="G654" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="655" spans="1:7" x14ac:dyDescent="0.25">
@@ -13309,7 +13309,7 @@
         <v>414</v>
       </c>
       <c r="G655" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="656" spans="1:7" x14ac:dyDescent="0.25">
@@ -13323,7 +13323,7 @@
         <v>415</v>
       </c>
       <c r="G656" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="657" spans="1:7" x14ac:dyDescent="0.25">
@@ -13337,7 +13337,7 @@
         <v>416</v>
       </c>
       <c r="G657" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="658" spans="1:7" x14ac:dyDescent="0.25">
@@ -13351,7 +13351,7 @@
         <v>417</v>
       </c>
       <c r="G658" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="659" spans="1:7" x14ac:dyDescent="0.25">
@@ -13365,7 +13365,7 @@
         <v>418</v>
       </c>
       <c r="G659" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="660" spans="1:7" x14ac:dyDescent="0.25">
@@ -13379,7 +13379,7 @@
         <v>419</v>
       </c>
       <c r="G660" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="661" spans="1:7" x14ac:dyDescent="0.25">
@@ -13393,7 +13393,7 @@
         <v>420</v>
       </c>
       <c r="G661" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="662" spans="1:7" x14ac:dyDescent="0.25">
@@ -13407,7 +13407,7 @@
         <v>421</v>
       </c>
       <c r="G662" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="663" spans="1:7" x14ac:dyDescent="0.25">
@@ -13421,7 +13421,7 @@
         <v>422</v>
       </c>
       <c r="G663" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="664" spans="1:7" x14ac:dyDescent="0.25">
@@ -13435,7 +13435,7 @@
         <v>423</v>
       </c>
       <c r="G664" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="665" spans="1:7" x14ac:dyDescent="0.25">
@@ -13449,7 +13449,7 @@
         <v>424</v>
       </c>
       <c r="G665" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="666" spans="1:7" x14ac:dyDescent="0.25">
@@ -13463,7 +13463,7 @@
         <v>425</v>
       </c>
       <c r="G666" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="667" spans="1:7" x14ac:dyDescent="0.25">
@@ -13477,7 +13477,7 @@
         <v>426</v>
       </c>
       <c r="G667" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="668" spans="1:7" x14ac:dyDescent="0.25">
@@ -13491,7 +13491,7 @@
         <v>427</v>
       </c>
       <c r="G668" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="669" spans="1:7" x14ac:dyDescent="0.25">
@@ -13505,7 +13505,7 @@
         <v>428</v>
       </c>
       <c r="G669" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="670" spans="1:7" x14ac:dyDescent="0.25">
@@ -13519,7 +13519,7 @@
         <v>429</v>
       </c>
       <c r="G670" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="671" spans="1:7" x14ac:dyDescent="0.25">
@@ -13533,7 +13533,7 @@
         <v>430</v>
       </c>
       <c r="G671" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="672" spans="1:7" x14ac:dyDescent="0.25">
@@ -13547,7 +13547,7 @@
         <v>431</v>
       </c>
       <c r="G672" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="673" spans="1:7" x14ac:dyDescent="0.25">
@@ -13561,7 +13561,7 @@
         <v>432</v>
       </c>
       <c r="G673" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="674" spans="1:7" x14ac:dyDescent="0.25">
@@ -13575,7 +13575,7 @@
         <v>433</v>
       </c>
       <c r="G674" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="675" spans="1:7" x14ac:dyDescent="0.25">
@@ -13589,7 +13589,7 @@
         <v>434</v>
       </c>
       <c r="G675" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="676" spans="1:7" x14ac:dyDescent="0.25">
@@ -13603,7 +13603,7 @@
         <v>435</v>
       </c>
       <c r="G676" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="677" spans="1:7" x14ac:dyDescent="0.25">
@@ -13617,7 +13617,7 @@
         <v>436</v>
       </c>
       <c r="G677" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="678" spans="1:7" x14ac:dyDescent="0.25">
@@ -13631,7 +13631,7 @@
         <v>437</v>
       </c>
       <c r="G678" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="679" spans="1:7" x14ac:dyDescent="0.25">
@@ -13645,7 +13645,7 @@
         <v>438</v>
       </c>
       <c r="G679" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="680" spans="1:7" x14ac:dyDescent="0.25">
@@ -13659,7 +13659,7 @@
         <v>439</v>
       </c>
       <c r="G680" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="681" spans="1:7" x14ac:dyDescent="0.25">
@@ -13673,7 +13673,7 @@
         <v>440</v>
       </c>
       <c r="G681" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="682" spans="1:7" x14ac:dyDescent="0.25">
@@ -13687,7 +13687,7 @@
         <v>441</v>
       </c>
       <c r="G682" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="683" spans="1:7" x14ac:dyDescent="0.25">
@@ -13701,7 +13701,7 @@
         <v>442</v>
       </c>
       <c r="G683" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="684" spans="1:7" x14ac:dyDescent="0.25">
@@ -13715,7 +13715,7 @@
         <v>443</v>
       </c>
       <c r="G684" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="685" spans="1:7" x14ac:dyDescent="0.25">
@@ -13729,7 +13729,7 @@
         <v>444</v>
       </c>
       <c r="G685" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="686" spans="1:7" x14ac:dyDescent="0.25">
@@ -13743,7 +13743,7 @@
         <v>445</v>
       </c>
       <c r="G686" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="687" spans="1:7" x14ac:dyDescent="0.25">
@@ -13757,7 +13757,7 @@
         <v>446</v>
       </c>
       <c r="G687" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="688" spans="1:7" x14ac:dyDescent="0.25">
@@ -13771,7 +13771,7 @@
         <v>447</v>
       </c>
       <c r="G688" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="689" spans="1:7" x14ac:dyDescent="0.25">
@@ -13785,7 +13785,7 @@
         <v>448</v>
       </c>
       <c r="G689" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="690" spans="1:7" x14ac:dyDescent="0.25">
@@ -13799,7 +13799,7 @@
         <v>449</v>
       </c>
       <c r="G690" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="691" spans="1:7" x14ac:dyDescent="0.25">
@@ -13813,7 +13813,7 @@
         <v>450</v>
       </c>
       <c r="G691" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="714" spans="7:7" x14ac:dyDescent="0.25">

--- a/SCH-STH/Impact assessments/Senegal/2025/november/sn_sppa_impact_2511_1_site.xlsx
+++ b/SCH-STH/Impact assessments/Senegal/2025/november/sn_sppa_impact_2511_1_site.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\SCH-STH\Impact assessments\Senegal\2025\november\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{249D69AE-C32E-4C55-BCC0-FC30B51DF225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E1F5446-EA86-4800-9E97-4238FB167B38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="498" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="498" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2551" uniqueCount="576">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2548" uniqueCount="576">
   <si>
     <t>type</t>
   </si>
@@ -1013,24 +1013,12 @@
     <t>bind::db_add_col_6</t>
   </si>
   <si>
-    <t>sn_sppa_impact_2511_1_site</t>
-  </si>
-  <si>
-    <t>(2025 Nov) - 1. SCH/STH – Site</t>
-  </si>
-  <si>
     <t>DAKAR</t>
   </si>
   <si>
     <t>KAOLACK</t>
   </si>
   <si>
-    <t>KEBEMER</t>
-  </si>
-  <si>
-    <t>LINGUERE</t>
-  </si>
-  <si>
     <t>MBACKE</t>
   </si>
   <si>
@@ -1905,6 +1893,18 @@
   </si>
   <si>
     <t>EP ALLOUWA D.OR</t>
+  </si>
+  <si>
+    <t>DIOURBEL</t>
+  </si>
+  <si>
+    <t>LOUGA</t>
+  </si>
+  <si>
+    <t>(2025 Nov) - 1. SCH/STH – Site V2</t>
+  </si>
+  <si>
+    <t>sn_sppa_impact_2511_1_site_v2</t>
   </si>
 </sst>
 </file>
@@ -3812,7 +3812,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G714"/>
+  <dimension ref="A1:G713"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.375" style="2" bestFit="1" customWidth="1"/>
@@ -4804,10 +4804,10 @@
         <v>198</v>
       </c>
       <c r="B84" s="20" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C84" s="17" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D84" s="17"/>
       <c r="E84" s="17"/>
@@ -4817,10 +4817,10 @@
         <v>198</v>
       </c>
       <c r="B85" s="17" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C85" s="17" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D85" s="17"/>
       <c r="E85" s="17"/>
@@ -4829,11 +4829,11 @@
       <c r="A86" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="B86" s="17" t="s">
-        <v>282</v>
-      </c>
-      <c r="C86" s="20" t="s">
-        <v>282</v>
+      <c r="B86" t="s">
+        <v>573</v>
+      </c>
+      <c r="C86" t="s">
+        <v>573</v>
       </c>
       <c r="D86" s="17"/>
       <c r="E86" s="17"/>
@@ -4842,33 +4842,35 @@
       <c r="A87" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="B87" s="17" t="s">
-        <v>283</v>
-      </c>
-      <c r="C87" s="20" t="s">
-        <v>283</v>
+      <c r="B87" t="s">
+        <v>572</v>
+      </c>
+      <c r="C87" t="s">
+        <v>572</v>
       </c>
       <c r="D87" s="17"/>
       <c r="E87" s="17"/>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="B88" s="17" t="s">
-        <v>284</v>
-      </c>
-      <c r="C88" s="20" t="s">
-        <v>284</v>
-      </c>
+      <c r="A88" s="16"/>
+      <c r="B88" s="17"/>
+      <c r="C88" s="20"/>
       <c r="D88" s="17"/>
       <c r="E88" s="17"/>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="16"/>
-      <c r="B89" s="17"/>
-      <c r="C89" s="20"/>
-      <c r="D89" s="17"/>
+      <c r="A89" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B89" s="17" t="s">
+        <v>281</v>
+      </c>
+      <c r="C89" s="17" t="s">
+        <v>281</v>
+      </c>
+      <c r="D89" s="17" t="s">
+        <v>278</v>
+      </c>
       <c r="E89" s="17"/>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -4876,13 +4878,13 @@
         <v>32</v>
       </c>
       <c r="B90" s="17" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C90" s="17" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D90" s="17" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E90" s="17"/>
     </row>
@@ -4891,13 +4893,13 @@
         <v>32</v>
       </c>
       <c r="B91" s="17" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C91" s="17" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D91" s="17" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E91" s="17"/>
     </row>
@@ -4906,13 +4908,13 @@
         <v>32</v>
       </c>
       <c r="B92" s="17" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C92" s="17" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D92" s="17" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E92" s="17"/>
     </row>
@@ -4921,13 +4923,13 @@
         <v>32</v>
       </c>
       <c r="B93" s="17" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="C93" s="17" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="D93" s="17" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E93" s="17"/>
     </row>
@@ -4936,13 +4938,13 @@
         <v>32</v>
       </c>
       <c r="B94" s="17" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C94" s="17" t="s">
-        <v>281</v>
-      </c>
-      <c r="D94" s="17" t="s">
-        <v>281</v>
+        <v>285</v>
+      </c>
+      <c r="D94" t="s">
+        <v>573</v>
       </c>
       <c r="E94" s="17"/>
     </row>
@@ -4951,13 +4953,13 @@
         <v>32</v>
       </c>
       <c r="B95" s="17" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C95" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="D95" s="17" t="s">
-        <v>282</v>
+        <v>286</v>
+      </c>
+      <c r="D95" t="s">
+        <v>573</v>
       </c>
       <c r="E95" s="17"/>
     </row>
@@ -4966,13 +4968,13 @@
         <v>32</v>
       </c>
       <c r="B96" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C96" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="D96" s="17" t="s">
-        <v>282</v>
+        <v>287</v>
+      </c>
+      <c r="D96" t="s">
+        <v>573</v>
       </c>
       <c r="E96" s="17"/>
     </row>
@@ -4981,13 +4983,13 @@
         <v>32</v>
       </c>
       <c r="B97" s="17" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="C97" s="17" t="s">
-        <v>291</v>
-      </c>
-      <c r="D97" s="17" t="s">
-        <v>283</v>
+        <v>280</v>
+      </c>
+      <c r="D97" t="s">
+        <v>572</v>
       </c>
       <c r="E97" s="17"/>
     </row>
@@ -4996,37 +4998,37 @@
         <v>32</v>
       </c>
       <c r="B98" s="17" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C98" s="17" t="s">
-        <v>284</v>
-      </c>
-      <c r="D98" s="17" t="s">
-        <v>284</v>
+        <v>288</v>
+      </c>
+      <c r="D98" t="s">
+        <v>572</v>
       </c>
       <c r="E98" s="17"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B99" s="17" t="s">
-        <v>292</v>
-      </c>
-      <c r="C99" s="17" t="s">
-        <v>292</v>
-      </c>
-      <c r="D99" s="17" t="s">
-        <v>284</v>
-      </c>
+      <c r="A99" s="16"/>
+      <c r="B99" s="17"/>
+      <c r="C99" s="17"/>
+      <c r="D99" s="17"/>
       <c r="E99" s="17"/>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="16"/>
-      <c r="B100" s="17"/>
-      <c r="C100" s="17"/>
+      <c r="A100" s="16" t="s">
+        <v>265</v>
+      </c>
+      <c r="B100" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="C100" s="17" t="s">
+        <v>266</v>
+      </c>
       <c r="D100" s="17"/>
-      <c r="E100" s="17"/>
+      <c r="E100" s="17" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="16" t="s">
@@ -5040,7 +5042,7 @@
       </c>
       <c r="D101" s="17"/>
       <c r="E101" s="17" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
@@ -5055,7 +5057,7 @@
       </c>
       <c r="D102" s="17"/>
       <c r="E102" s="17" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -5070,7 +5072,7 @@
       </c>
       <c r="D103" s="17"/>
       <c r="E103" s="17" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
@@ -5085,7 +5087,7 @@
       </c>
       <c r="D104" s="17"/>
       <c r="E104" s="17" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -5100,7 +5102,7 @@
       </c>
       <c r="D105" s="17"/>
       <c r="E105" s="17" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -5115,7 +5117,7 @@
       </c>
       <c r="D106" s="17"/>
       <c r="E106" s="17" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -5130,7 +5132,7 @@
       </c>
       <c r="D107" s="17"/>
       <c r="E107" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -5145,7 +5147,7 @@
       </c>
       <c r="D108" s="17"/>
       <c r="E108" s="17" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
@@ -5160,44 +5162,44 @@
       </c>
       <c r="D109" s="17"/>
       <c r="E109" s="17" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" s="16" t="s">
-        <v>265</v>
-      </c>
-      <c r="B110" s="17" t="s">
-        <v>266</v>
-      </c>
-      <c r="C110" s="17" t="s">
-        <v>266</v>
-      </c>
+      <c r="A110" s="16"/>
+      <c r="B110" s="17"/>
+      <c r="C110" s="17"/>
       <c r="D110" s="17"/>
-      <c r="E110" s="17" t="s">
-        <v>292</v>
-      </c>
+      <c r="E110" s="17"/>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" s="16"/>
-      <c r="B111" s="17"/>
-      <c r="C111" s="17"/>
-      <c r="D111" s="17"/>
-      <c r="E111" s="17"/>
+      <c r="A111" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B111" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="C111" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="D111" s="22"/>
+      <c r="E111" s="19" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="16" t="s">
         <v>33</v>
       </c>
       <c r="B112" s="22" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C112" s="22" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D112" s="22"/>
       <c r="E112" s="19" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
@@ -5205,14 +5207,14 @@
         <v>33</v>
       </c>
       <c r="B113" s="22" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C113" s="22" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D113" s="22"/>
       <c r="E113" s="19" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
@@ -5220,14 +5222,14 @@
         <v>33</v>
       </c>
       <c r="B114" s="22" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C114" s="22" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D114" s="22"/>
       <c r="E114" s="19" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
@@ -5235,14 +5237,14 @@
         <v>33</v>
       </c>
       <c r="B115" s="22" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C115" s="22" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D115" s="22"/>
       <c r="E115" s="19" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
@@ -5250,14 +5252,14 @@
         <v>33</v>
       </c>
       <c r="B116" s="22" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C116" s="22" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="D116" s="22"/>
       <c r="E116" s="19" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
@@ -5265,14 +5267,14 @@
         <v>33</v>
       </c>
       <c r="B117" s="22" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C117" s="22" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D117" s="22"/>
       <c r="E117" s="19" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
@@ -5280,14 +5282,14 @@
         <v>33</v>
       </c>
       <c r="B118" s="22" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C118" s="22" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="D118" s="22"/>
       <c r="E118" s="19" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
@@ -5295,14 +5297,14 @@
         <v>33</v>
       </c>
       <c r="B119" s="22" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C119" s="22" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="D119" s="22"/>
       <c r="E119" s="19" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
@@ -5310,14 +5312,14 @@
         <v>33</v>
       </c>
       <c r="B120" s="22" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C120" s="22" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D120" s="22"/>
       <c r="E120" s="19" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
@@ -5325,14 +5327,14 @@
         <v>33</v>
       </c>
       <c r="B121" s="22" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C121" s="22" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D121" s="22"/>
       <c r="E121" s="19" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
@@ -5340,14 +5342,14 @@
         <v>33</v>
       </c>
       <c r="B122" s="22" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C122" s="22" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D122" s="22"/>
       <c r="E122" s="19" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
@@ -5355,14 +5357,14 @@
         <v>33</v>
       </c>
       <c r="B123" s="22" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C123" s="22" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D123" s="22"/>
       <c r="E123" s="19" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
@@ -5370,14 +5372,14 @@
         <v>33</v>
       </c>
       <c r="B124" s="22" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C124" s="22" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D124" s="22"/>
       <c r="E124" s="19" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
@@ -5385,14 +5387,14 @@
         <v>33</v>
       </c>
       <c r="B125" s="22" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C125" s="22" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D125" s="22"/>
       <c r="E125" s="19" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
@@ -5400,14 +5402,14 @@
         <v>33</v>
       </c>
       <c r="B126" s="22" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C126" s="22" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D126" s="22"/>
       <c r="E126" s="19" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
@@ -5415,14 +5417,14 @@
         <v>33</v>
       </c>
       <c r="B127" s="22" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C127" s="22" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D127" s="22"/>
       <c r="E127" s="19" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
@@ -5430,14 +5432,14 @@
         <v>33</v>
       </c>
       <c r="B128" s="22" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C128" s="22" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D128" s="22"/>
       <c r="E128" s="19" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
@@ -5445,14 +5447,14 @@
         <v>33</v>
       </c>
       <c r="B129" s="22" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C129" s="22" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D129" s="22"/>
       <c r="E129" s="19" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
@@ -5460,14 +5462,14 @@
         <v>33</v>
       </c>
       <c r="B130" s="22" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C130" s="22" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D130" s="22"/>
       <c r="E130" s="19" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
@@ -5475,14 +5477,14 @@
         <v>33</v>
       </c>
       <c r="B131" s="22" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C131" s="22" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="D131" s="22"/>
       <c r="E131" s="19" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
@@ -5490,14 +5492,14 @@
         <v>33</v>
       </c>
       <c r="B132" s="22" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C132" s="22" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D132" s="22"/>
       <c r="E132" s="19" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
@@ -5505,14 +5507,14 @@
         <v>33</v>
       </c>
       <c r="B133" s="22" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C133" s="22" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D133" s="22"/>
       <c r="E133" s="19" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
@@ -5520,14 +5522,14 @@
         <v>33</v>
       </c>
       <c r="B134" s="22" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C134" s="22" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="D134" s="22"/>
       <c r="E134" s="19" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
@@ -5535,14 +5537,14 @@
         <v>33</v>
       </c>
       <c r="B135" s="22" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C135" s="22" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D135" s="22"/>
       <c r="E135" s="19" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
@@ -5550,14 +5552,14 @@
         <v>33</v>
       </c>
       <c r="B136" s="22" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C136" s="22" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D136" s="22"/>
       <c r="E136" s="19" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
@@ -5565,44 +5567,44 @@
         <v>33</v>
       </c>
       <c r="B137" s="22" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C137" s="22" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D137" s="22"/>
       <c r="E137" s="19" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A138" s="16" t="s">
         <v>33</v>
       </c>
       <c r="B138" s="22" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C138" s="22" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D138" s="22"/>
       <c r="E138" s="19" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="16" t="s">
         <v>33</v>
       </c>
       <c r="B139" s="22" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C139" s="22" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D139" s="22"/>
       <c r="E139" s="19" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
@@ -5610,29 +5612,29 @@
         <v>33</v>
       </c>
       <c r="B140" s="22" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C140" s="22" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D140" s="22"/>
       <c r="E140" s="19" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A141" s="16" t="s">
         <v>33</v>
       </c>
       <c r="B141" s="22" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C141" s="22" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D141" s="22"/>
       <c r="E141" s="19" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -5640,29 +5642,29 @@
         <v>33</v>
       </c>
       <c r="B142" s="22" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C142" s="22" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D142" s="22"/>
       <c r="E142" s="19" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="16" t="s">
         <v>33</v>
       </c>
       <c r="B143" s="22" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C143" s="22" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D143" s="22"/>
       <c r="E143" s="19" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
@@ -5670,14 +5672,14 @@
         <v>33</v>
       </c>
       <c r="B144" s="22" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C144" s="22" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D144" s="22"/>
       <c r="E144" s="19" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
@@ -5685,14 +5687,14 @@
         <v>33</v>
       </c>
       <c r="B145" s="22" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C145" s="22" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="D145" s="22"/>
       <c r="E145" s="19" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
@@ -5700,14 +5702,14 @@
         <v>33</v>
       </c>
       <c r="B146" s="22" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C146" s="22" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="D146" s="22"/>
       <c r="E146" s="19" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
@@ -5715,14 +5717,14 @@
         <v>33</v>
       </c>
       <c r="B147" s="22" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C147" s="22" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D147" s="22"/>
       <c r="E147" s="19" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
@@ -5730,14 +5732,14 @@
         <v>33</v>
       </c>
       <c r="B148" s="22" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C148" s="22" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="D148" s="22"/>
       <c r="E148" s="19" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
@@ -5745,14 +5747,14 @@
         <v>33</v>
       </c>
       <c r="B149" s="22" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C149" s="22" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D149" s="22"/>
       <c r="E149" s="19" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
@@ -5760,14 +5762,14 @@
         <v>33</v>
       </c>
       <c r="B150" s="22" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C150" s="22" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D150" s="22"/>
       <c r="E150" s="19" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
@@ -5775,14 +5777,14 @@
         <v>33</v>
       </c>
       <c r="B151" s="22" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C151" s="22" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D151" s="22"/>
       <c r="E151" s="19" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
@@ -5790,14 +5792,14 @@
         <v>33</v>
       </c>
       <c r="B152" s="22" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C152" s="22" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D152" s="22"/>
       <c r="E152" s="19" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
@@ -5805,14 +5807,14 @@
         <v>33</v>
       </c>
       <c r="B153" s="22" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C153" s="22" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D153" s="22"/>
       <c r="E153" s="19" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
@@ -5820,14 +5822,14 @@
         <v>33</v>
       </c>
       <c r="B154" s="22" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C154" s="22" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D154" s="22"/>
       <c r="E154" s="19" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
@@ -5835,14 +5837,14 @@
         <v>33</v>
       </c>
       <c r="B155" s="22" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C155" s="22" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="D155" s="22"/>
       <c r="E155" s="19" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
@@ -5850,14 +5852,14 @@
         <v>33</v>
       </c>
       <c r="B156" s="22" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C156" s="22" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="D156" s="22"/>
       <c r="E156" s="19" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
@@ -5865,14 +5867,14 @@
         <v>33</v>
       </c>
       <c r="B157" s="22" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C157" s="22" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D157" s="22"/>
       <c r="E157" s="19" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
@@ -5880,14 +5882,14 @@
         <v>33</v>
       </c>
       <c r="B158" s="22" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C158" s="22" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="D158" s="22"/>
       <c r="E158" s="19" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
@@ -5895,14 +5897,14 @@
         <v>33</v>
       </c>
       <c r="B159" s="22" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C159" s="22" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D159" s="22"/>
       <c r="E159" s="19" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
@@ -5910,14 +5912,14 @@
         <v>33</v>
       </c>
       <c r="B160" s="22" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C160" s="22" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D160" s="22"/>
       <c r="E160" s="19" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
@@ -5925,14 +5927,14 @@
         <v>33</v>
       </c>
       <c r="B161" s="22" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C161" s="22" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D161" s="22"/>
       <c r="E161" s="19" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
@@ -5940,14 +5942,14 @@
         <v>33</v>
       </c>
       <c r="B162" s="22" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C162" s="22" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D162" s="22"/>
       <c r="E162" s="19" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
@@ -5955,14 +5957,14 @@
         <v>33</v>
       </c>
       <c r="B163" s="22" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C163" s="22" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D163" s="22"/>
       <c r="E163" s="19" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
@@ -5970,14 +5972,14 @@
         <v>33</v>
       </c>
       <c r="B164" s="22" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C164" s="22" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="D164" s="22"/>
       <c r="E164" s="19" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
@@ -5985,14 +5987,14 @@
         <v>33</v>
       </c>
       <c r="B165" s="22" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C165" s="22" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="D165" s="22"/>
       <c r="E165" s="19" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
@@ -6000,14 +6002,14 @@
         <v>33</v>
       </c>
       <c r="B166" s="22" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C166" s="22" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="D166" s="22"/>
       <c r="E166" s="19" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
@@ -6015,14 +6017,14 @@
         <v>33</v>
       </c>
       <c r="B167" s="22" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C167" s="22" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D167" s="22"/>
       <c r="E167" s="19" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
@@ -6030,14 +6032,14 @@
         <v>33</v>
       </c>
       <c r="B168" s="22" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C168" s="22" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D168" s="22"/>
       <c r="E168" s="19" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
@@ -6045,14 +6047,14 @@
         <v>33</v>
       </c>
       <c r="B169" s="22" t="s">
-        <v>350</v>
+        <v>570</v>
       </c>
       <c r="C169" s="22" t="s">
-        <v>350</v>
+        <v>570</v>
       </c>
       <c r="D169" s="22"/>
       <c r="E169" s="19" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
@@ -6060,14 +6062,14 @@
         <v>33</v>
       </c>
       <c r="B170" s="22" t="s">
-        <v>574</v>
+        <v>347</v>
       </c>
       <c r="C170" s="22" t="s">
-        <v>574</v>
+        <v>347</v>
       </c>
       <c r="D170" s="22"/>
       <c r="E170" s="19" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
@@ -6075,14 +6077,14 @@
         <v>33</v>
       </c>
       <c r="B171" s="22" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C171" s="22" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D171" s="22"/>
       <c r="E171" s="19" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
@@ -6090,14 +6092,14 @@
         <v>33</v>
       </c>
       <c r="B172" s="22" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C172" s="22" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="D172" s="22"/>
       <c r="E172" s="19" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
@@ -6105,14 +6107,14 @@
         <v>33</v>
       </c>
       <c r="B173" s="22" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C173" s="22" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D173" s="22"/>
       <c r="E173" s="19" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
@@ -6120,14 +6122,14 @@
         <v>33</v>
       </c>
       <c r="B174" s="22" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C174" s="22" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D174" s="22"/>
       <c r="E174" s="19" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
@@ -6135,14 +6137,14 @@
         <v>33</v>
       </c>
       <c r="B175" s="22" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C175" s="22" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D175" s="22"/>
       <c r="E175" s="19" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
@@ -6150,14 +6152,14 @@
         <v>33</v>
       </c>
       <c r="B176" s="22" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C176" s="22" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D176" s="22"/>
       <c r="E176" s="19" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
@@ -6165,14 +6167,14 @@
         <v>33</v>
       </c>
       <c r="B177" s="22" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C177" s="22" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D177" s="22"/>
       <c r="E177" s="19" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
@@ -6180,14 +6182,14 @@
         <v>33</v>
       </c>
       <c r="B178" s="22" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C178" s="22" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="D178" s="22"/>
       <c r="E178" s="19" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
@@ -6195,14 +6197,14 @@
         <v>33</v>
       </c>
       <c r="B179" s="22" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C179" s="22" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="D179" s="22"/>
       <c r="E179" s="19" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
@@ -6210,14 +6212,14 @@
         <v>33</v>
       </c>
       <c r="B180" s="22" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C180" s="22" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="D180" s="22"/>
       <c r="E180" s="19" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
@@ -6225,14 +6227,14 @@
         <v>33</v>
       </c>
       <c r="B181" s="22" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C181" s="22" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="D181" s="22"/>
       <c r="E181" s="19" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
@@ -6240,14 +6242,14 @@
         <v>33</v>
       </c>
       <c r="B182" s="22" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C182" s="22" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="D182" s="22"/>
       <c r="E182" s="19" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
@@ -6255,14 +6257,14 @@
         <v>33</v>
       </c>
       <c r="B183" s="22" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C183" s="22" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D183" s="22"/>
       <c r="E183" s="19" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
@@ -6270,14 +6272,14 @@
         <v>33</v>
       </c>
       <c r="B184" s="22" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C184" s="22" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="D184" s="22"/>
       <c r="E184" s="19" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
@@ -6285,14 +6287,14 @@
         <v>33</v>
       </c>
       <c r="B185" s="22" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C185" s="22" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="D185" s="22"/>
       <c r="E185" s="19" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
@@ -6300,14 +6302,14 @@
         <v>33</v>
       </c>
       <c r="B186" s="22" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C186" s="22" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="D186" s="22"/>
       <c r="E186" s="19" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
@@ -6315,14 +6317,14 @@
         <v>33</v>
       </c>
       <c r="B187" s="22" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C187" s="22" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="D187" s="22"/>
       <c r="E187" s="19" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
@@ -6330,14 +6332,14 @@
         <v>33</v>
       </c>
       <c r="B188" s="22" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C188" s="22" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="D188" s="22"/>
       <c r="E188" s="19" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
@@ -6345,14 +6347,14 @@
         <v>33</v>
       </c>
       <c r="B189" s="22" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C189" s="22" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="D189" s="22"/>
       <c r="E189" s="19" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
@@ -6360,14 +6362,14 @@
         <v>33</v>
       </c>
       <c r="B190" s="22" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C190" s="22" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="D190" s="22"/>
       <c r="E190" s="19" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
@@ -6375,14 +6377,14 @@
         <v>33</v>
       </c>
       <c r="B191" s="22" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C191" s="22" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D191" s="22"/>
       <c r="E191" s="19" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
@@ -6390,14 +6392,14 @@
         <v>33</v>
       </c>
       <c r="B192" s="22" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C192" s="22" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="D192" s="22"/>
       <c r="E192" s="19" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
@@ -6405,14 +6407,14 @@
         <v>33</v>
       </c>
       <c r="B193" s="22" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C193" s="22" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="D193" s="22"/>
       <c r="E193" s="19" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
@@ -6420,14 +6422,14 @@
         <v>33</v>
       </c>
       <c r="B194" s="22" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C194" s="22" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="D194" s="22"/>
       <c r="E194" s="19" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
@@ -6435,14 +6437,14 @@
         <v>33</v>
       </c>
       <c r="B195" s="22" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C195" s="22" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D195" s="22"/>
       <c r="E195" s="19" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
@@ -6450,14 +6452,14 @@
         <v>33</v>
       </c>
       <c r="B196" s="22" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C196" s="22" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="D196" s="22"/>
       <c r="E196" s="19" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
@@ -6465,14 +6467,14 @@
         <v>33</v>
       </c>
       <c r="B197" s="22" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C197" s="22" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="D197" s="22"/>
       <c r="E197" s="19" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
@@ -6480,14 +6482,14 @@
         <v>33</v>
       </c>
       <c r="B198" s="22" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C198" s="22" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D198" s="22"/>
       <c r="E198" s="19" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
@@ -6495,14 +6497,14 @@
         <v>33</v>
       </c>
       <c r="B199" s="22" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C199" s="22" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="D199" s="22"/>
       <c r="E199" s="19" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
@@ -6510,14 +6512,14 @@
         <v>33</v>
       </c>
       <c r="B200" s="22" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C200" s="22" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="D200" s="22"/>
       <c r="E200" s="19" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
@@ -6525,14 +6527,14 @@
         <v>33</v>
       </c>
       <c r="B201" s="22" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C201" s="22" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D201" s="22"/>
       <c r="E201" s="19" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
@@ -6540,14 +6542,14 @@
         <v>33</v>
       </c>
       <c r="B202" s="22" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C202" s="22" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="D202" s="22"/>
       <c r="E202" s="19" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
@@ -6555,14 +6557,14 @@
         <v>33</v>
       </c>
       <c r="B203" s="22" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C203" s="22" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D203" s="22"/>
       <c r="E203" s="19" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
@@ -6570,14 +6572,14 @@
         <v>33</v>
       </c>
       <c r="B204" s="22" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C204" s="22" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D204" s="22"/>
       <c r="E204" s="19" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
@@ -6585,14 +6587,14 @@
         <v>33</v>
       </c>
       <c r="B205" s="22" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C205" s="22" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D205" s="22"/>
       <c r="E205" s="19" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
@@ -6600,14 +6602,14 @@
         <v>33</v>
       </c>
       <c r="B206" s="22" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C206" s="22" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D206" s="22"/>
       <c r="E206" s="19" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
@@ -6615,14 +6617,14 @@
         <v>33</v>
       </c>
       <c r="B207" s="22" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C207" s="22" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D207" s="22"/>
       <c r="E207" s="19" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
@@ -6630,14 +6632,14 @@
         <v>33</v>
       </c>
       <c r="B208" s="22" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C208" s="22" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="D208" s="22"/>
       <c r="E208" s="19" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
@@ -6645,14 +6647,14 @@
         <v>33</v>
       </c>
       <c r="B209" s="22" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C209" s="22" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D209" s="22"/>
       <c r="E209" s="19" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
@@ -6660,14 +6662,14 @@
         <v>33</v>
       </c>
       <c r="B210" s="22" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C210" s="22" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="D210" s="22"/>
       <c r="E210" s="19" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
@@ -6675,14 +6677,14 @@
         <v>33</v>
       </c>
       <c r="B211" s="22" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C211" s="22" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="D211" s="22"/>
       <c r="E211" s="19" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
@@ -6690,14 +6692,14 @@
         <v>33</v>
       </c>
       <c r="B212" s="22" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C212" s="22" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D212" s="22"/>
       <c r="E212" s="19" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
@@ -6705,14 +6707,14 @@
         <v>33</v>
       </c>
       <c r="B213" s="22" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C213" s="22" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="D213" s="22"/>
       <c r="E213" s="19" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
@@ -6720,14 +6722,14 @@
         <v>33</v>
       </c>
       <c r="B214" s="22" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C214" s="22" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="D214" s="22"/>
       <c r="E214" s="19" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
@@ -6735,14 +6737,14 @@
         <v>33</v>
       </c>
       <c r="B215" s="22" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C215" s="22" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D215" s="22"/>
       <c r="E215" s="19" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
@@ -6750,14 +6752,14 @@
         <v>33</v>
       </c>
       <c r="B216" s="22" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C216" s="22" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="D216" s="22"/>
       <c r="E216" s="19" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
@@ -6765,14 +6767,14 @@
         <v>33</v>
       </c>
       <c r="B217" s="22" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C217" s="22" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="D217" s="22"/>
       <c r="E217" s="19" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
@@ -6780,14 +6782,14 @@
         <v>33</v>
       </c>
       <c r="B218" s="22" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C218" s="22" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="D218" s="22"/>
       <c r="E218" s="19" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
@@ -6795,14 +6797,14 @@
         <v>33</v>
       </c>
       <c r="B219" s="22" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C219" s="22" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="D219" s="22"/>
       <c r="E219" s="19" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
@@ -6810,14 +6812,14 @@
         <v>33</v>
       </c>
       <c r="B220" s="22" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C220" s="22" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="D220" s="22"/>
       <c r="E220" s="19" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
@@ -6825,14 +6827,14 @@
         <v>33</v>
       </c>
       <c r="B221" s="22" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C221" s="22" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="D221" s="22"/>
       <c r="E221" s="19" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
@@ -6840,14 +6842,14 @@
         <v>33</v>
       </c>
       <c r="B222" s="22" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C222" s="22" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="D222" s="22"/>
       <c r="E222" s="19" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
@@ -6855,14 +6857,14 @@
         <v>33</v>
       </c>
       <c r="B223" s="22" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C223" s="22" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="D223" s="22"/>
       <c r="E223" s="19" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
@@ -6870,14 +6872,14 @@
         <v>33</v>
       </c>
       <c r="B224" s="22" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C224" s="22" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="D224" s="22"/>
       <c r="E224" s="19" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
@@ -6885,14 +6887,14 @@
         <v>33</v>
       </c>
       <c r="B225" s="22" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C225" s="22" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="D225" s="22"/>
       <c r="E225" s="19" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
@@ -6900,14 +6902,14 @@
         <v>33</v>
       </c>
       <c r="B226" s="22" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C226" s="22" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="D226" s="22"/>
       <c r="E226" s="19" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
@@ -6915,14 +6917,14 @@
         <v>33</v>
       </c>
       <c r="B227" s="22" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C227" s="22" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D227" s="22"/>
       <c r="E227" s="19" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
@@ -6930,14 +6932,14 @@
         <v>33</v>
       </c>
       <c r="B228" s="22" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C228" s="22" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="D228" s="22"/>
       <c r="E228" s="19" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
@@ -6945,14 +6947,14 @@
         <v>33</v>
       </c>
       <c r="B229" s="22" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C229" s="22" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D229" s="22"/>
       <c r="E229" s="19" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
@@ -6960,14 +6962,14 @@
         <v>33</v>
       </c>
       <c r="B230" s="22" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C230" s="22" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="D230" s="22"/>
       <c r="E230" s="19" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
@@ -6975,14 +6977,14 @@
         <v>33</v>
       </c>
       <c r="B231" s="22" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C231" s="22" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="D231" s="22"/>
       <c r="E231" s="19" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
@@ -6990,14 +6992,14 @@
         <v>33</v>
       </c>
       <c r="B232" s="22" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C232" s="22" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="D232" s="22"/>
       <c r="E232" s="19" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
@@ -7005,14 +7007,14 @@
         <v>33</v>
       </c>
       <c r="B233" s="22" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C233" s="22" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="D233" s="22"/>
       <c r="E233" s="19" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
@@ -7020,14 +7022,14 @@
         <v>33</v>
       </c>
       <c r="B234" s="22" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C234" s="22" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D234" s="22"/>
       <c r="E234" s="19" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
@@ -7035,14 +7037,14 @@
         <v>33</v>
       </c>
       <c r="B235" s="22" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C235" s="22" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="D235" s="22"/>
       <c r="E235" s="19" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.25">
@@ -7050,14 +7052,14 @@
         <v>33</v>
       </c>
       <c r="B236" s="22" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C236" s="22" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="D236" s="22"/>
       <c r="E236" s="19" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.25">
@@ -7065,14 +7067,14 @@
         <v>33</v>
       </c>
       <c r="B237" s="22" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C237" s="22" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="D237" s="22"/>
       <c r="E237" s="19" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.25">
@@ -7080,14 +7082,14 @@
         <v>33</v>
       </c>
       <c r="B238" s="22" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C238" s="22" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="D238" s="22"/>
       <c r="E238" s="19" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.25">
@@ -7095,14 +7097,14 @@
         <v>33</v>
       </c>
       <c r="B239" s="22" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C239" s="22" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D239" s="22"/>
       <c r="E239" s="19" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.25">
@@ -7110,92 +7112,92 @@
         <v>33</v>
       </c>
       <c r="B240" s="22" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C240" s="22" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="D240" s="22"/>
       <c r="E240" s="19" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="16" t="s">
         <v>33</v>
       </c>
       <c r="B241" s="22" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C241" s="22" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="D241" s="22"/>
       <c r="E241" s="19" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="16" t="s">
         <v>33</v>
       </c>
       <c r="B242" s="22" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C242" s="22" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="D242" s="22"/>
       <c r="E242" s="19" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="16" t="s">
         <v>33</v>
       </c>
       <c r="B243" s="22" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C243" s="22" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D243" s="22"/>
       <c r="E243" s="19" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="16" t="s">
         <v>33</v>
       </c>
       <c r="B244" s="22" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C244" s="22" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="D244" s="22"/>
       <c r="E244" s="19" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="16" t="s">
         <v>33</v>
       </c>
       <c r="B245" s="22" t="s">
-        <v>425</v>
+        <v>233</v>
       </c>
       <c r="C245" s="22" t="s">
-        <v>425</v>
+        <v>233</v>
       </c>
       <c r="D245" s="22"/>
       <c r="E245" s="19" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="16" t="s">
         <v>33</v>
       </c>
@@ -7207,10 +7209,10 @@
       </c>
       <c r="D246" s="22"/>
       <c r="E246" s="19" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="16" t="s">
         <v>33</v>
       </c>
@@ -7222,10 +7224,10 @@
       </c>
       <c r="D247" s="22"/>
       <c r="E247" s="19" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="16" t="s">
         <v>33</v>
       </c>
@@ -7237,10 +7239,10 @@
       </c>
       <c r="D248" s="22"/>
       <c r="E248" s="19" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="16" t="s">
         <v>33</v>
       </c>
@@ -7252,10 +7254,10 @@
       </c>
       <c r="D249" s="22"/>
       <c r="E249" s="19" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="16" t="s">
         <v>33</v>
       </c>
@@ -7267,10 +7269,10 @@
       </c>
       <c r="D250" s="22"/>
       <c r="E250" s="19" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="16" t="s">
         <v>33</v>
       </c>
@@ -7282,10 +7284,10 @@
       </c>
       <c r="D251" s="22"/>
       <c r="E251" s="19" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="16" t="s">
         <v>33</v>
       </c>
@@ -7297,10 +7299,10 @@
       </c>
       <c r="D252" s="22"/>
       <c r="E252" s="19" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="16" t="s">
         <v>33</v>
       </c>
@@ -7312,10 +7314,10 @@
       </c>
       <c r="D253" s="22"/>
       <c r="E253" s="19" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="16" t="s">
         <v>33</v>
       </c>
@@ -7327,44 +7329,44 @@
       </c>
       <c r="D254" s="22"/>
       <c r="E254" s="19" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A255" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="B255" s="22" t="s">
-        <v>233</v>
-      </c>
-      <c r="C255" s="22" t="s">
-        <v>233</v>
-      </c>
+        <v>288</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A255" s="16"/>
+      <c r="B255" s="22"/>
+      <c r="C255" s="22"/>
       <c r="D255" s="22"/>
-      <c r="E255" s="19" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A256" s="16"/>
-      <c r="B256" s="22"/>
-      <c r="C256" s="22"/>
-      <c r="D256" s="22"/>
-      <c r="E256" s="19"/>
+      <c r="E255" s="19"/>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A256" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B256" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C256" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="D256" s="3"/>
+      <c r="F256" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="D257" s="3"/>
       <c r="F257" t="s">
-        <v>352</v>
+        <v>377</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -7372,14 +7374,14 @@
         <v>73</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="D258" s="3"/>
       <c r="F258" t="s">
-        <v>381</v>
+        <v>316</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -7387,14 +7389,14 @@
         <v>73</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D259" s="3"/>
       <c r="F259" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -7402,14 +7404,14 @@
         <v>73</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="D260" s="3"/>
       <c r="F260" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -7417,44 +7419,44 @@
         <v>73</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C261" s="3" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D261" s="3"/>
       <c r="F261" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C262" s="3" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D262" s="3"/>
       <c r="F262" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="263" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C263" s="3" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="D263" s="3"/>
       <c r="F263" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -7462,14 +7464,14 @@
         <v>73</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="D264" s="3"/>
       <c r="F264" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -7477,44 +7479,44 @@
         <v>73</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C265" s="3" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D265" s="3"/>
       <c r="F265" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B266" s="3" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C266" s="3" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="D266" s="3"/>
       <c r="F266" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="267" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C267" s="3" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D267" s="3"/>
       <c r="F267" t="s">
-        <v>411</v>
+        <v>349</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -7522,29 +7524,29 @@
         <v>73</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C268" s="3" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D268" s="3"/>
       <c r="F268" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C269" s="3" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D269" s="3"/>
       <c r="F269" t="s">
-        <v>353</v>
+        <v>408</v>
       </c>
     </row>
     <row r="270" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
@@ -7552,29 +7554,29 @@
         <v>73</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C270" s="3" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="D270" s="3"/>
       <c r="F270" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="271" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D271" s="3"/>
       <c r="F271" t="s">
-        <v>293</v>
+        <v>362</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
@@ -7582,14 +7584,14 @@
         <v>73</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C272" s="3" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D272" s="3"/>
       <c r="F272" t="s">
-        <v>366</v>
+        <v>290</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
@@ -7597,14 +7599,14 @@
         <v>73</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C273" s="3" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="D273" s="3"/>
       <c r="F273" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
@@ -7612,14 +7614,14 @@
         <v>73</v>
       </c>
       <c r="B274" s="3" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C274" s="3" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="D274" s="3"/>
       <c r="F274" t="s">
-        <v>294</v>
+        <v>378</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
@@ -7627,14 +7629,14 @@
         <v>73</v>
       </c>
       <c r="B275" s="3" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C275" s="3" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="D275" s="3"/>
       <c r="F275" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -7642,14 +7644,14 @@
         <v>73</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C276" s="3" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="D276" s="3"/>
       <c r="F276" t="s">
-        <v>367</v>
+        <v>291</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
@@ -7657,14 +7659,14 @@
         <v>73</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C277" s="3" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D277" s="3"/>
       <c r="F277" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
@@ -7672,14 +7674,14 @@
         <v>73</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C278" s="3" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="D278" s="3"/>
       <c r="F278" t="s">
-        <v>296</v>
+        <v>350</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
@@ -7687,44 +7689,44 @@
         <v>73</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C279" s="3" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D279" s="3"/>
       <c r="F279" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C280" s="3" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D280" s="3"/>
       <c r="F280" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="281" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C281" s="3" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="D281" s="3"/>
       <c r="F281" t="s">
-        <v>413</v>
+        <v>330</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
@@ -7732,44 +7734,44 @@
         <v>73</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C282" s="3" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="D282" s="3"/>
       <c r="F282" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C283" s="3" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="D283" s="3"/>
       <c r="F283" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="284" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C284" s="3" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="D284" s="3"/>
       <c r="F284" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
@@ -7777,14 +7779,14 @@
         <v>73</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C285" s="3" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="D285" s="3"/>
       <c r="F285" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
@@ -7792,14 +7794,14 @@
         <v>73</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C286" s="3" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D286" s="3"/>
       <c r="F286" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
@@ -7807,14 +7809,14 @@
         <v>73</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C287" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="D287" s="3"/>
       <c r="F287" t="s">
-        <v>346</v>
+        <v>392</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
@@ -7822,14 +7824,14 @@
         <v>73</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C288" s="3" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="D288" s="3"/>
       <c r="F288" t="s">
-        <v>396</v>
+        <v>351</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -7837,14 +7839,14 @@
         <v>73</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C289" s="3" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="D289" s="3"/>
       <c r="F289" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -7852,29 +7854,29 @@
         <v>73</v>
       </c>
       <c r="B290" s="3" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C290" s="3" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="D290" s="3"/>
       <c r="F290" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C291" s="3" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="D291" s="3"/>
       <c r="F291" t="s">
-        <v>357</v>
+        <v>393</v>
       </c>
     </row>
     <row r="292" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
@@ -7882,29 +7884,29 @@
         <v>73</v>
       </c>
       <c r="B292" s="3" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C292" s="3" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D292" s="3"/>
       <c r="F292" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="293" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>462</v>
+        <v>395</v>
       </c>
       <c r="C293" s="3" t="s">
-        <v>462</v>
+        <v>395</v>
       </c>
       <c r="D293" s="3"/>
       <c r="F293" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -7912,44 +7914,44 @@
         <v>73</v>
       </c>
       <c r="B294" s="3" t="s">
-        <v>399</v>
+        <v>459</v>
       </c>
       <c r="C294" s="3" t="s">
-        <v>399</v>
+        <v>459</v>
       </c>
       <c r="D294" s="3"/>
       <c r="F294" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C295" s="3" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="D295" s="3"/>
       <c r="F295" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="296" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B296" s="3" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D296" s="3"/>
       <c r="F296" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -7957,44 +7959,44 @@
         <v>73</v>
       </c>
       <c r="B297" s="3" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C297" s="3" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="D297" s="3"/>
       <c r="F297" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B298" s="3" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="C298" s="3" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="D298" s="3"/>
       <c r="F298" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="299" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B299" s="3" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C299" s="3" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D299" s="3"/>
       <c r="F299" t="s">
-        <v>359</v>
+        <v>381</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -8002,14 +8004,14 @@
         <v>73</v>
       </c>
       <c r="B300" s="3" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="C300" s="3" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="D300" s="3"/>
       <c r="F300" t="s">
-        <v>385</v>
+        <v>293</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
@@ -8017,14 +8019,14 @@
         <v>73</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="C301" s="3" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D301" s="3"/>
       <c r="F301" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
@@ -8032,14 +8034,14 @@
         <v>73</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C302" s="3" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="D302" s="3"/>
       <c r="F302" t="s">
-        <v>297</v>
+        <v>397</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
@@ -8047,14 +8049,14 @@
         <v>73</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C303" s="3" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="D303" s="3"/>
       <c r="F303" t="s">
-        <v>401</v>
+        <v>382</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
@@ -8062,14 +8064,14 @@
         <v>73</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C304" s="3" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D304" s="3"/>
       <c r="F304" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
@@ -8077,14 +8079,14 @@
         <v>73</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="C305" s="3" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="D305" s="3"/>
       <c r="F305" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
@@ -8092,14 +8094,14 @@
         <v>73</v>
       </c>
       <c r="B306" s="3" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="C306" s="3" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D306" s="3"/>
       <c r="F306" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
@@ -8107,14 +8109,14 @@
         <v>73</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="C307" s="3" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="D307" s="3"/>
       <c r="F307" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
@@ -8122,14 +8124,14 @@
         <v>73</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C308" s="3" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D308" s="3"/>
       <c r="F308" t="s">
-        <v>403</v>
+        <v>356</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
@@ -8137,29 +8139,29 @@
         <v>73</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C309" s="3" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="D309" s="3"/>
       <c r="F309" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B310" s="3" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C310" s="3" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="D310" s="3"/>
       <c r="F310" t="s">
-        <v>404</v>
+        <v>385</v>
       </c>
     </row>
     <row r="311" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
@@ -8167,29 +8169,29 @@
         <v>73</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="C311" s="3" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D311" s="3"/>
       <c r="F311" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="312" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="C312" s="3" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="D312" s="3"/>
       <c r="F312" t="s">
-        <v>405</v>
+        <v>386</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
@@ -8197,14 +8199,14 @@
         <v>73</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C313" s="3" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="D313" s="3"/>
       <c r="F313" t="s">
-        <v>390</v>
+        <v>357</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
@@ -8212,14 +8214,14 @@
         <v>73</v>
       </c>
       <c r="B314" s="3" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C314" s="3" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="D314" s="3"/>
       <c r="F314" t="s">
-        <v>361</v>
+        <v>402</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
@@ -8227,14 +8229,14 @@
         <v>73</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="C315" s="3" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="D315" s="3"/>
       <c r="F315" t="s">
-        <v>406</v>
+        <v>387</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
@@ -8242,14 +8244,14 @@
         <v>73</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C316" s="3" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="D316" s="3"/>
       <c r="F316" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
@@ -8257,14 +8259,14 @@
         <v>73</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C317" s="3" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D317" s="3"/>
       <c r="F317" t="s">
-        <v>407</v>
+        <v>319</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
@@ -8272,44 +8274,44 @@
         <v>73</v>
       </c>
       <c r="B318" s="3" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C318" s="3" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="D318" s="3"/>
       <c r="F318" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C319" s="3" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="D319" s="3"/>
       <c r="F319" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="320" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B320" s="3" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C320" s="3" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="D320" s="3"/>
       <c r="F320" t="s">
-        <v>336</v>
+        <v>410</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
@@ -8317,14 +8319,14 @@
         <v>73</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C321" s="3" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="D321" s="3"/>
       <c r="F321" t="s">
-        <v>414</v>
+        <v>364</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
@@ -8332,29 +8334,29 @@
         <v>73</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C322" s="3" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="D322" s="3"/>
       <c r="F322" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C323" s="3" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D323" s="3"/>
       <c r="F323" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="324" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
@@ -8362,14 +8364,14 @@
         <v>73</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C324" s="3" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="D324" s="3"/>
       <c r="F324" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="325" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
@@ -8377,29 +8379,29 @@
         <v>73</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C325" s="3" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="D325" s="3"/>
       <c r="F325" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="326" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="C326" s="3" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="D326" s="3"/>
       <c r="F326" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
@@ -8407,14 +8409,14 @@
         <v>73</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C327" s="3" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="D327" s="3"/>
       <c r="F327" t="s">
-        <v>338</v>
+        <v>303</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
@@ -8422,74 +8424,74 @@
         <v>73</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C328" s="3" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D328" s="3"/>
       <c r="F328" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C329" s="3" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="D329" s="3"/>
       <c r="F329" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="330" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C330" s="3" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="D330" s="3"/>
       <c r="F330" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C331" s="3" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="D331" s="3"/>
       <c r="F331" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="332" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B332" s="3" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="C332" s="3" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D332" s="3"/>
       <c r="F332" t="s">
-        <v>308</v>
+        <v>295</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
@@ -8497,14 +8499,14 @@
         <v>73</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="C333" s="3" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D333" s="3"/>
       <c r="F333" t="s">
-        <v>299</v>
+        <v>365</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
@@ -8512,44 +8514,44 @@
         <v>73</v>
       </c>
       <c r="B334" s="3" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="C334" s="3" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="D334" s="3"/>
       <c r="F334" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6" ht="63" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C335" s="3" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="D335" s="3"/>
       <c r="F335" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="336" spans="1:6" ht="63" x14ac:dyDescent="0.25">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B336" s="3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="C336" s="3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="D336" s="3"/>
       <c r="F336" t="s">
-        <v>339</v>
+        <v>366</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
@@ -8557,14 +8559,14 @@
         <v>73</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C337" s="3" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D337" s="3"/>
       <c r="F337" t="s">
-        <v>370</v>
+        <v>296</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
@@ -8572,14 +8574,14 @@
         <v>73</v>
       </c>
       <c r="B338" s="3" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D338" s="3"/>
       <c r="F338" t="s">
-        <v>300</v>
+        <v>343</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
@@ -8587,29 +8589,29 @@
         <v>73</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="D339" s="3"/>
       <c r="F339" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="C340" s="3" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D340" s="3"/>
       <c r="F340" t="s">
-        <v>325</v>
+        <v>297</v>
       </c>
     </row>
     <row r="341" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
@@ -8617,14 +8619,14 @@
         <v>73</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="C341" s="3" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="D341" s="3"/>
       <c r="F341" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="342" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
@@ -8632,29 +8634,29 @@
         <v>73</v>
       </c>
       <c r="B342" s="3" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="C342" s="3" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D342" s="3"/>
       <c r="F342" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="343" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B343" s="3" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="C343" s="3" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="D343" s="3"/>
       <c r="F343" t="s">
-        <v>418</v>
+        <v>344</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
@@ -8662,14 +8664,14 @@
         <v>73</v>
       </c>
       <c r="B344" s="3" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="C344" s="3" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="D344" s="3"/>
       <c r="F344" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
@@ -8677,14 +8679,14 @@
         <v>73</v>
       </c>
       <c r="B345" s="3" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C345" s="3" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D345" s="3"/>
       <c r="F345" t="s">
-        <v>348</v>
+        <v>367</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
@@ -8692,14 +8694,14 @@
         <v>73</v>
       </c>
       <c r="B346" s="3" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C346" s="3" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D346" s="3"/>
       <c r="F346" t="s">
-        <v>371</v>
+        <v>305</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
@@ -8707,14 +8709,14 @@
         <v>73</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="C347" s="3" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D347" s="3"/>
       <c r="F347" t="s">
-        <v>309</v>
+        <v>368</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
@@ -8722,14 +8724,14 @@
         <v>73</v>
       </c>
       <c r="B348" s="3" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="C348" s="3" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D348" s="3"/>
       <c r="F348" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
@@ -8737,44 +8739,44 @@
         <v>73</v>
       </c>
       <c r="B349" s="3" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="C349" s="3" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D349" s="3"/>
       <c r="F349" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B350" s="3" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="C350" s="3" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D350" s="3"/>
       <c r="F350" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="351" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="C351" s="3" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="D351" s="3"/>
       <c r="F351" t="s">
-        <v>340</v>
+        <v>299</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
@@ -8782,59 +8784,59 @@
         <v>73</v>
       </c>
       <c r="B352" s="3" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C352" s="3" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D352" s="3"/>
       <c r="F352" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B353" s="3" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="C353" s="3" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D353" s="3"/>
       <c r="F353" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="354" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B354" s="3" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="C354" s="3" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="D354" s="3"/>
       <c r="F354" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B355" s="3" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="C355" s="3" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="D355" s="3"/>
       <c r="F355" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="356" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
@@ -8842,29 +8844,29 @@
         <v>73</v>
       </c>
       <c r="B356" s="3" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="C356" s="3" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D356" s="3"/>
       <c r="F356" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="357" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B357" s="3" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="C357" s="3" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="D357" s="3"/>
       <c r="F357" t="s">
-        <v>313</v>
+        <v>337</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.25">
@@ -8872,14 +8874,14 @@
         <v>73</v>
       </c>
       <c r="B358" s="3" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="C358" s="3" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D358" s="3"/>
       <c r="F358" t="s">
-        <v>341</v>
+        <v>370</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.25">
@@ -8887,14 +8889,14 @@
         <v>73</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="C359" s="3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="D359" s="3"/>
       <c r="F359" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.25">
@@ -8902,14 +8904,14 @@
         <v>73</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="C360" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="D360" s="3"/>
       <c r="F360" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.25">
@@ -8917,14 +8919,14 @@
         <v>73</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="C361" s="3" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="D361" s="3"/>
       <c r="F361" t="s">
-        <v>376</v>
+        <v>416</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.25">
@@ -8932,14 +8934,14 @@
         <v>73</v>
       </c>
       <c r="B362" s="3" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="C362" s="3" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="D362" s="3"/>
       <c r="F362" t="s">
-        <v>420</v>
+        <v>310</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.25">
@@ -8947,14 +8949,14 @@
         <v>73</v>
       </c>
       <c r="B363" s="3" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="C363" s="3" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="D363" s="3"/>
       <c r="F363" t="s">
-        <v>314</v>
+        <v>373</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.25">
@@ -8962,14 +8964,14 @@
         <v>73</v>
       </c>
       <c r="B364" s="3" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="C364" s="3" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="D364" s="3"/>
       <c r="F364" t="s">
-        <v>377</v>
+        <v>323</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.25">
@@ -8977,14 +8979,14 @@
         <v>73</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="C365" s="3" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="D365" s="3"/>
       <c r="F365" t="s">
-        <v>327</v>
+        <v>345</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
@@ -8992,14 +8994,14 @@
         <v>73</v>
       </c>
       <c r="B366" s="3" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="C366" s="3" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="D366" s="3"/>
       <c r="F366" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.25">
@@ -9007,14 +9009,14 @@
         <v>73</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="C367" s="3" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="D367" s="3"/>
       <c r="F367" t="s">
-        <v>349</v>
+        <v>374</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.25">
@@ -9022,14 +9024,14 @@
         <v>73</v>
       </c>
       <c r="B368" s="3" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="C368" s="3" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="D368" s="3"/>
       <c r="F368" t="s">
-        <v>378</v>
+        <v>311</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.25">
@@ -9037,14 +9039,14 @@
         <v>73</v>
       </c>
       <c r="B369" s="3" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="C369" s="3" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="D369" s="3"/>
       <c r="F369" t="s">
-        <v>315</v>
+        <v>346</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.25">
@@ -9052,14 +9054,14 @@
         <v>73</v>
       </c>
       <c r="B370" s="3" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="C370" s="3" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="D370" s="3"/>
       <c r="F370" t="s">
-        <v>350</v>
+        <v>570</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.25">
@@ -9067,14 +9069,14 @@
         <v>73</v>
       </c>
       <c r="B371" s="3" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="C371" s="3" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="D371" s="3"/>
       <c r="F371" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.25">
@@ -9082,44 +9084,44 @@
         <v>73</v>
       </c>
       <c r="B372" s="3" t="s">
-        <v>540</v>
+        <v>571</v>
       </c>
       <c r="C372" s="3" t="s">
-        <v>540</v>
+        <v>571</v>
       </c>
       <c r="D372" s="3"/>
       <c r="F372" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="373" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>575</v>
+        <v>537</v>
       </c>
       <c r="C373" s="3" t="s">
-        <v>575</v>
+        <v>537</v>
       </c>
       <c r="D373" s="3"/>
       <c r="F373" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="374" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B374" s="3" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="C374" s="3" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="D374" s="3"/>
       <c r="F374" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
@@ -9127,14 +9129,14 @@
         <v>73</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="C375" s="3" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="D375" s="3"/>
       <c r="F375" t="s">
-        <v>351</v>
+        <v>312</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.25">
@@ -9142,14 +9144,14 @@
         <v>73</v>
       </c>
       <c r="B376" s="3" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="C376" s="3" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="D376" s="3"/>
       <c r="F376" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.25">
@@ -9157,14 +9159,14 @@
         <v>73</v>
       </c>
       <c r="B377" s="3" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="C377" s="3" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="D377" s="3"/>
       <c r="F377" t="s">
-        <v>317</v>
+        <v>418</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.25">
@@ -9172,14 +9174,14 @@
         <v>73</v>
       </c>
       <c r="B378" s="3" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="C378" s="3" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="D378" s="3"/>
       <c r="F378" t="s">
-        <v>422</v>
+        <v>375</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
@@ -9187,14 +9189,14 @@
         <v>73</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="C379" s="3" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="D379" s="3"/>
       <c r="F379" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.25">
@@ -9202,14 +9204,14 @@
         <v>73</v>
       </c>
       <c r="B380" s="3" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="C380" s="3" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="D380" s="3"/>
       <c r="F380" t="s">
-        <v>380</v>
+        <v>419</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.25">
@@ -9217,14 +9219,14 @@
         <v>73</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="C381" s="3" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D381" s="3"/>
       <c r="F381" t="s">
-        <v>423</v>
+        <v>338</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.25">
@@ -9232,44 +9234,44 @@
         <v>73</v>
       </c>
       <c r="B382" s="3" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="C382" s="3" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="D382" s="3"/>
       <c r="F382" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.25">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="383" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="C383" s="3" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="D383" s="3"/>
       <c r="F383" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="384" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="384" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B384" s="3" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="C384" s="3" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="D384" s="3"/>
       <c r="F384" t="s">
-        <v>425</v>
+        <v>324</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.25">
@@ -9277,14 +9279,14 @@
         <v>73</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="C385" s="3" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="D385" s="3"/>
       <c r="F385" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.25">
@@ -9292,14 +9294,14 @@
         <v>73</v>
       </c>
       <c r="B386" s="3" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="C386" s="3" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="D386" s="3"/>
       <c r="F386" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.25">
@@ -9307,14 +9309,14 @@
         <v>73</v>
       </c>
       <c r="B387" s="3" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="C387" s="3" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="D387" s="3"/>
       <c r="F387" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.25">
@@ -9322,14 +9324,14 @@
         <v>73</v>
       </c>
       <c r="B388" s="3" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="C388" s="3" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="D388" s="3"/>
       <c r="F388" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.25">
@@ -9337,14 +9339,14 @@
         <v>73</v>
       </c>
       <c r="B389" s="3" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="C389" s="3" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D389" s="3"/>
       <c r="F389" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.25">
@@ -9352,14 +9354,14 @@
         <v>73</v>
       </c>
       <c r="B390" s="3" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C390" s="3" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="D390" s="3"/>
       <c r="F390" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.25">
@@ -9367,14 +9369,14 @@
         <v>73</v>
       </c>
       <c r="B391" s="3" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="C391" s="3" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D391" s="3"/>
       <c r="F391" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.25">
@@ -9382,14 +9384,14 @@
         <v>73</v>
       </c>
       <c r="B392" s="3" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="C392" s="3" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="D392" s="3"/>
       <c r="F392" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.25">
@@ -9397,14 +9399,14 @@
         <v>73</v>
       </c>
       <c r="B393" s="3" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="C393" s="3" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D393" s="3"/>
       <c r="F393" t="s">
-        <v>343</v>
+        <v>300</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.25">
@@ -9412,14 +9414,14 @@
         <v>73</v>
       </c>
       <c r="B394" s="3" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="C394" s="3" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="D394" s="3"/>
       <c r="F394" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.25">
@@ -9427,14 +9429,14 @@
         <v>73</v>
       </c>
       <c r="B395" s="3" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="C395" s="3" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="D395" s="3"/>
       <c r="F395" t="s">
-        <v>319</v>
+        <v>388</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.25">
@@ -9442,14 +9444,14 @@
         <v>73</v>
       </c>
       <c r="B396" s="3" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="C396" s="3" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="D396" s="3"/>
       <c r="F396" t="s">
-        <v>392</v>
+        <v>358</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.25">
@@ -9457,14 +9459,14 @@
         <v>73</v>
       </c>
       <c r="B397" s="3" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="C397" s="3" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="D397" s="3"/>
       <c r="F397" t="s">
-        <v>362</v>
+        <v>404</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.25">
@@ -9472,14 +9474,14 @@
         <v>73</v>
       </c>
       <c r="B398" s="3" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="C398" s="3" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="D398" s="3"/>
       <c r="F398" t="s">
-        <v>408</v>
+        <v>359</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.25">
@@ -9487,44 +9489,44 @@
         <v>73</v>
       </c>
       <c r="B399" s="3" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="C399" s="3" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D399" s="3"/>
       <c r="F399" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.25">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="400" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B400" s="3" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="C400" s="3" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="D400" s="3"/>
       <c r="F400" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="401" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="401" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B401" s="3" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="C401" s="3" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="D401" s="3"/>
       <c r="F401" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.25">
@@ -9532,14 +9534,14 @@
         <v>73</v>
       </c>
       <c r="B402" s="3" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="C402" s="3" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="D402" s="3"/>
       <c r="F402" t="s">
-        <v>409</v>
+        <v>360</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.25">
@@ -9547,14 +9549,14 @@
         <v>73</v>
       </c>
       <c r="B403" s="3" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="C403" s="3" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="D403" s="3"/>
       <c r="F403" t="s">
-        <v>364</v>
+        <v>391</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.25">
@@ -9562,14 +9564,14 @@
         <v>73</v>
       </c>
       <c r="B404" s="3" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="C404" s="3" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="D404" s="3"/>
       <c r="F404" t="s">
-        <v>395</v>
+        <v>406</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.25">
@@ -9577,14 +9579,14 @@
         <v>73</v>
       </c>
       <c r="B405" s="3" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C405" s="3" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="D405" s="3"/>
       <c r="F405" t="s">
-        <v>410</v>
+        <v>361</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.25">
@@ -9592,14 +9594,14 @@
         <v>73</v>
       </c>
       <c r="B406" s="3" t="s">
-        <v>573</v>
+        <v>233</v>
       </c>
       <c r="C406" s="3" t="s">
-        <v>573</v>
+        <v>233</v>
       </c>
       <c r="D406" s="3"/>
       <c r="F406" t="s">
-        <v>365</v>
+        <v>289</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.25">
@@ -9614,7 +9616,7 @@
       </c>
       <c r="D407" s="3"/>
       <c r="F407" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.25">
@@ -9629,7 +9631,7 @@
       </c>
       <c r="D408" s="3"/>
       <c r="F408" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.25">
@@ -9644,7 +9646,7 @@
       </c>
       <c r="D409" s="3"/>
       <c r="F409" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.25">
@@ -9659,7 +9661,7 @@
       </c>
       <c r="D410" s="3"/>
       <c r="F410" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.25">
@@ -9674,7 +9676,7 @@
       </c>
       <c r="D411" s="3"/>
       <c r="F411" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.25">
@@ -9689,7 +9691,7 @@
       </c>
       <c r="D412" s="3"/>
       <c r="F412" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.25">
@@ -9704,7 +9706,7 @@
       </c>
       <c r="D413" s="3"/>
       <c r="F413" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.25">
@@ -9719,7 +9721,7 @@
       </c>
       <c r="D414" s="3"/>
       <c r="F414" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.25">
@@ -9734,7 +9736,7 @@
       </c>
       <c r="D415" s="3"/>
       <c r="F415" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.25">
@@ -9749,7 +9751,7 @@
       </c>
       <c r="D416" s="3"/>
       <c r="F416" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.25">
@@ -9764,7 +9766,7 @@
       </c>
       <c r="D417" s="3"/>
       <c r="F417" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.25">
@@ -9779,7 +9781,7 @@
       </c>
       <c r="D418" s="3"/>
       <c r="F418" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.25">
@@ -9794,7 +9796,7 @@
       </c>
       <c r="D419" s="3"/>
       <c r="F419" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.25">
@@ -9809,7 +9811,7 @@
       </c>
       <c r="D420" s="3"/>
       <c r="F420" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.25">
@@ -9824,7 +9826,7 @@
       </c>
       <c r="D421" s="3"/>
       <c r="F421" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.25">
@@ -9839,7 +9841,7 @@
       </c>
       <c r="D422" s="3"/>
       <c r="F422" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.25">
@@ -9854,7 +9856,7 @@
       </c>
       <c r="D423" s="3"/>
       <c r="F423" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.25">
@@ -9869,7 +9871,7 @@
       </c>
       <c r="D424" s="3"/>
       <c r="F424" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.25">
@@ -9884,7 +9886,7 @@
       </c>
       <c r="D425" s="3"/>
       <c r="F425" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.25">
@@ -9899,7 +9901,7 @@
       </c>
       <c r="D426" s="3"/>
       <c r="F426" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.25">
@@ -9914,7 +9916,7 @@
       </c>
       <c r="D427" s="3"/>
       <c r="F427" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.25">
@@ -9929,7 +9931,7 @@
       </c>
       <c r="D428" s="3"/>
       <c r="F428" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.25">
@@ -9944,7 +9946,7 @@
       </c>
       <c r="D429" s="3"/>
       <c r="F429" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.25">
@@ -9959,7 +9961,7 @@
       </c>
       <c r="D430" s="3"/>
       <c r="F430" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.25">
@@ -9974,7 +9976,7 @@
       </c>
       <c r="D431" s="3"/>
       <c r="F431" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.25">
@@ -9989,7 +9991,7 @@
       </c>
       <c r="D432" s="3"/>
       <c r="F432" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.25">
@@ -10004,7 +10006,7 @@
       </c>
       <c r="D433" s="3"/>
       <c r="F433" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.25">
@@ -10019,7 +10021,7 @@
       </c>
       <c r="D434" s="3"/>
       <c r="F434" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.25">
@@ -10034,7 +10036,7 @@
       </c>
       <c r="D435" s="3"/>
       <c r="F435" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.25">
@@ -10049,7 +10051,7 @@
       </c>
       <c r="D436" s="3"/>
       <c r="F436" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.25">
@@ -10064,7 +10066,7 @@
       </c>
       <c r="D437" s="3"/>
       <c r="F437" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.25">
@@ -10079,7 +10081,7 @@
       </c>
       <c r="D438" s="3"/>
       <c r="F438" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.25">
@@ -10094,7 +10096,7 @@
       </c>
       <c r="D439" s="3"/>
       <c r="F439" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.25">
@@ -10109,7 +10111,7 @@
       </c>
       <c r="D440" s="3"/>
       <c r="F440" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.25">
@@ -10124,7 +10126,7 @@
       </c>
       <c r="D441" s="3"/>
       <c r="F441" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.25">
@@ -10139,7 +10141,7 @@
       </c>
       <c r="D442" s="3"/>
       <c r="F442" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.25">
@@ -10154,7 +10156,7 @@
       </c>
       <c r="D443" s="3"/>
       <c r="F443" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.25">
@@ -10169,7 +10171,7 @@
       </c>
       <c r="D444" s="3"/>
       <c r="F444" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.25">
@@ -10184,7 +10186,7 @@
       </c>
       <c r="D445" s="3"/>
       <c r="F445" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.25">
@@ -10199,7 +10201,7 @@
       </c>
       <c r="D446" s="3"/>
       <c r="F446" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.25">
@@ -10214,7 +10216,7 @@
       </c>
       <c r="D447" s="3"/>
       <c r="F447" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.25">
@@ -10229,7 +10231,7 @@
       </c>
       <c r="D448" s="3"/>
       <c r="F448" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.25">
@@ -10244,7 +10246,7 @@
       </c>
       <c r="D449" s="3"/>
       <c r="F449" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.25">
@@ -10259,7 +10261,7 @@
       </c>
       <c r="D450" s="3"/>
       <c r="F450" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.25">
@@ -10274,7 +10276,7 @@
       </c>
       <c r="D451" s="3"/>
       <c r="F451" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.25">
@@ -10289,7 +10291,7 @@
       </c>
       <c r="D452" s="3"/>
       <c r="F452" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.25">
@@ -10304,7 +10306,7 @@
       </c>
       <c r="D453" s="3"/>
       <c r="F453" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.25">
@@ -10319,7 +10321,7 @@
       </c>
       <c r="D454" s="3"/>
       <c r="F454" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.25">
@@ -10334,7 +10336,7 @@
       </c>
       <c r="D455" s="3"/>
       <c r="F455" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.25">
@@ -10349,7 +10351,7 @@
       </c>
       <c r="D456" s="3"/>
       <c r="F456" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.25">
@@ -10364,7 +10366,7 @@
       </c>
       <c r="D457" s="3"/>
       <c r="F457" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.25">
@@ -10379,7 +10381,7 @@
       </c>
       <c r="D458" s="3"/>
       <c r="F458" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.25">
@@ -10394,7 +10396,7 @@
       </c>
       <c r="D459" s="3"/>
       <c r="F459" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.25">
@@ -10409,7 +10411,7 @@
       </c>
       <c r="D460" s="3"/>
       <c r="F460" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.25">
@@ -10424,7 +10426,7 @@
       </c>
       <c r="D461" s="3"/>
       <c r="F461" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.25">
@@ -10439,7 +10441,7 @@
       </c>
       <c r="D462" s="3"/>
       <c r="F462" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.25">
@@ -10454,7 +10456,7 @@
       </c>
       <c r="D463" s="3"/>
       <c r="F463" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.25">
@@ -10469,7 +10471,7 @@
       </c>
       <c r="D464" s="3"/>
       <c r="F464" t="s">
-        <v>350</v>
+        <v>570</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.25">
@@ -10484,7 +10486,7 @@
       </c>
       <c r="D465" s="3"/>
       <c r="F465" t="s">
-        <v>574</v>
+        <v>347</v>
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.25">
@@ -10499,7 +10501,7 @@
       </c>
       <c r="D466" s="3"/>
       <c r="F466" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.25">
@@ -10514,7 +10516,7 @@
       </c>
       <c r="D467" s="3"/>
       <c r="F467" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.25">
@@ -10529,7 +10531,7 @@
       </c>
       <c r="D468" s="3"/>
       <c r="F468" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.25">
@@ -10544,7 +10546,7 @@
       </c>
       <c r="D469" s="3"/>
       <c r="F469" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.25">
@@ -10559,7 +10561,7 @@
       </c>
       <c r="D470" s="3"/>
       <c r="F470" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.25">
@@ -10574,7 +10576,7 @@
       </c>
       <c r="D471" s="3"/>
       <c r="F471" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.25">
@@ -10589,7 +10591,7 @@
       </c>
       <c r="D472" s="3"/>
       <c r="F472" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.25">
@@ -10604,7 +10606,7 @@
       </c>
       <c r="D473" s="3"/>
       <c r="F473" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.25">
@@ -10619,7 +10621,7 @@
       </c>
       <c r="D474" s="3"/>
       <c r="F474" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.25">
@@ -10634,7 +10636,7 @@
       </c>
       <c r="D475" s="3"/>
       <c r="F475" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.25">
@@ -10649,7 +10651,7 @@
       </c>
       <c r="D476" s="3"/>
       <c r="F476" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.25">
@@ -10664,7 +10666,7 @@
       </c>
       <c r="D477" s="3"/>
       <c r="F477" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.25">
@@ -10679,7 +10681,7 @@
       </c>
       <c r="D478" s="3"/>
       <c r="F478" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.25">
@@ -10694,7 +10696,7 @@
       </c>
       <c r="D479" s="3"/>
       <c r="F479" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.25">
@@ -10709,7 +10711,7 @@
       </c>
       <c r="D480" s="3"/>
       <c r="F480" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.25">
@@ -10724,7 +10726,7 @@
       </c>
       <c r="D481" s="3"/>
       <c r="F481" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.25">
@@ -10739,7 +10741,7 @@
       </c>
       <c r="D482" s="3"/>
       <c r="F482" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.25">
@@ -10754,7 +10756,7 @@
       </c>
       <c r="D483" s="3"/>
       <c r="F483" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.25">
@@ -10769,7 +10771,7 @@
       </c>
       <c r="D484" s="3"/>
       <c r="F484" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.25">
@@ -10784,7 +10786,7 @@
       </c>
       <c r="D485" s="3"/>
       <c r="F485" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.25">
@@ -10799,7 +10801,7 @@
       </c>
       <c r="D486" s="3"/>
       <c r="F486" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.25">
@@ -10814,7 +10816,7 @@
       </c>
       <c r="D487" s="3"/>
       <c r="F487" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.25">
@@ -10829,7 +10831,7 @@
       </c>
       <c r="D488" s="3"/>
       <c r="F488" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.25">
@@ -10844,7 +10846,7 @@
       </c>
       <c r="D489" s="3"/>
       <c r="F489" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.25">
@@ -10859,7 +10861,7 @@
       </c>
       <c r="D490" s="3"/>
       <c r="F490" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.25">
@@ -10874,7 +10876,7 @@
       </c>
       <c r="D491" s="3"/>
       <c r="F491" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.25">
@@ -10889,7 +10891,7 @@
       </c>
       <c r="D492" s="3"/>
       <c r="F492" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.25">
@@ -10904,7 +10906,7 @@
       </c>
       <c r="D493" s="3"/>
       <c r="F493" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.25">
@@ -10919,7 +10921,7 @@
       </c>
       <c r="D494" s="3"/>
       <c r="F494" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.25">
@@ -10934,7 +10936,7 @@
       </c>
       <c r="D495" s="3"/>
       <c r="F495" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.25">
@@ -10949,7 +10951,7 @@
       </c>
       <c r="D496" s="3"/>
       <c r="F496" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.25">
@@ -10964,7 +10966,7 @@
       </c>
       <c r="D497" s="3"/>
       <c r="F497" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.25">
@@ -10979,7 +10981,7 @@
       </c>
       <c r="D498" s="3"/>
       <c r="F498" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.25">
@@ -10994,7 +10996,7 @@
       </c>
       <c r="D499" s="3"/>
       <c r="F499" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="500" spans="1:6" x14ac:dyDescent="0.25">
@@ -11009,7 +11011,7 @@
       </c>
       <c r="D500" s="3"/>
       <c r="F500" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="501" spans="1:6" x14ac:dyDescent="0.25">
@@ -11024,7 +11026,7 @@
       </c>
       <c r="D501" s="3"/>
       <c r="F501" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.25">
@@ -11039,7 +11041,7 @@
       </c>
       <c r="D502" s="3"/>
       <c r="F502" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.25">
@@ -11054,7 +11056,7 @@
       </c>
       <c r="D503" s="3"/>
       <c r="F503" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="504" spans="1:6" x14ac:dyDescent="0.25">
@@ -11069,7 +11071,7 @@
       </c>
       <c r="D504" s="3"/>
       <c r="F504" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.25">
@@ -11084,7 +11086,7 @@
       </c>
       <c r="D505" s="3"/>
       <c r="F505" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="506" spans="1:6" x14ac:dyDescent="0.25">
@@ -11099,7 +11101,7 @@
       </c>
       <c r="D506" s="3"/>
       <c r="F506" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="507" spans="1:6" x14ac:dyDescent="0.25">
@@ -11114,7 +11116,7 @@
       </c>
       <c r="D507" s="3"/>
       <c r="F507" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="508" spans="1:6" x14ac:dyDescent="0.25">
@@ -11129,7 +11131,7 @@
       </c>
       <c r="D508" s="3"/>
       <c r="F508" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="509" spans="1:6" x14ac:dyDescent="0.25">
@@ -11144,7 +11146,7 @@
       </c>
       <c r="D509" s="3"/>
       <c r="F509" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="510" spans="1:6" x14ac:dyDescent="0.25">
@@ -11159,7 +11161,7 @@
       </c>
       <c r="D510" s="3"/>
       <c r="F510" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="511" spans="1:6" x14ac:dyDescent="0.25">
@@ -11174,7 +11176,7 @@
       </c>
       <c r="D511" s="3"/>
       <c r="F511" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="512" spans="1:6" x14ac:dyDescent="0.25">
@@ -11189,7 +11191,7 @@
       </c>
       <c r="D512" s="3"/>
       <c r="F512" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="513" spans="1:6" x14ac:dyDescent="0.25">
@@ -11204,7 +11206,7 @@
       </c>
       <c r="D513" s="3"/>
       <c r="F513" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="514" spans="1:6" x14ac:dyDescent="0.25">
@@ -11219,7 +11221,7 @@
       </c>
       <c r="D514" s="3"/>
       <c r="F514" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="515" spans="1:6" x14ac:dyDescent="0.25">
@@ -11234,7 +11236,7 @@
       </c>
       <c r="D515" s="3"/>
       <c r="F515" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="516" spans="1:6" x14ac:dyDescent="0.25">
@@ -11249,7 +11251,7 @@
       </c>
       <c r="D516" s="3"/>
       <c r="F516" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="517" spans="1:6" x14ac:dyDescent="0.25">
@@ -11264,7 +11266,7 @@
       </c>
       <c r="D517" s="3"/>
       <c r="F517" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="518" spans="1:6" x14ac:dyDescent="0.25">
@@ -11279,7 +11281,7 @@
       </c>
       <c r="D518" s="3"/>
       <c r="F518" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="519" spans="1:6" x14ac:dyDescent="0.25">
@@ -11294,7 +11296,7 @@
       </c>
       <c r="D519" s="3"/>
       <c r="F519" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="520" spans="1:6" x14ac:dyDescent="0.25">
@@ -11309,7 +11311,7 @@
       </c>
       <c r="D520" s="3"/>
       <c r="F520" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="521" spans="1:6" x14ac:dyDescent="0.25">
@@ -11324,7 +11326,7 @@
       </c>
       <c r="D521" s="3"/>
       <c r="F521" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="522" spans="1:6" x14ac:dyDescent="0.25">
@@ -11339,7 +11341,7 @@
       </c>
       <c r="D522" s="3"/>
       <c r="F522" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="523" spans="1:6" x14ac:dyDescent="0.25">
@@ -11354,7 +11356,7 @@
       </c>
       <c r="D523" s="3"/>
       <c r="F523" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
     <row r="524" spans="1:6" x14ac:dyDescent="0.25">
@@ -11369,7 +11371,7 @@
       </c>
       <c r="D524" s="3"/>
       <c r="F524" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="525" spans="1:6" x14ac:dyDescent="0.25">
@@ -11384,7 +11386,7 @@
       </c>
       <c r="D525" s="3"/>
       <c r="F525" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="526" spans="1:6" x14ac:dyDescent="0.25">
@@ -11399,7 +11401,7 @@
       </c>
       <c r="D526" s="3"/>
       <c r="F526" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="527" spans="1:6" x14ac:dyDescent="0.25">
@@ -11414,7 +11416,7 @@
       </c>
       <c r="D527" s="3"/>
       <c r="F527" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="528" spans="1:6" x14ac:dyDescent="0.25">
@@ -11429,7 +11431,7 @@
       </c>
       <c r="D528" s="3"/>
       <c r="F528" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="529" spans="1:7" x14ac:dyDescent="0.25">
@@ -11444,7 +11446,7 @@
       </c>
       <c r="D529" s="3"/>
       <c r="F529" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="530" spans="1:7" x14ac:dyDescent="0.25">
@@ -11459,7 +11461,7 @@
       </c>
       <c r="D530" s="3"/>
       <c r="F530" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="531" spans="1:7" x14ac:dyDescent="0.25">
@@ -11474,7 +11476,7 @@
       </c>
       <c r="D531" s="3"/>
       <c r="F531" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="532" spans="1:7" x14ac:dyDescent="0.25">
@@ -11489,7 +11491,7 @@
       </c>
       <c r="D532" s="3"/>
       <c r="F532" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="533" spans="1:7" x14ac:dyDescent="0.25">
@@ -11504,7 +11506,7 @@
       </c>
       <c r="D533" s="3"/>
       <c r="F533" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="534" spans="1:7" x14ac:dyDescent="0.25">
@@ -11519,7 +11521,7 @@
       </c>
       <c r="D534" s="3"/>
       <c r="F534" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="535" spans="1:7" x14ac:dyDescent="0.25">
@@ -11534,7 +11536,7 @@
       </c>
       <c r="D535" s="3"/>
       <c r="F535" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="536" spans="1:7" x14ac:dyDescent="0.25">
@@ -11549,7 +11551,7 @@
       </c>
       <c r="D536" s="3"/>
       <c r="F536" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="537" spans="1:7" x14ac:dyDescent="0.25">
@@ -11564,7 +11566,7 @@
       </c>
       <c r="D537" s="3"/>
       <c r="F537" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="538" spans="1:7" x14ac:dyDescent="0.25">
@@ -11579,7 +11581,7 @@
       </c>
       <c r="D538" s="3"/>
       <c r="F538" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="539" spans="1:7" x14ac:dyDescent="0.25">
@@ -11594,42 +11596,42 @@
       </c>
       <c r="D539" s="3"/>
       <c r="F539" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="540" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A540" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B540" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="C540" s="3" t="s">
-        <v>233</v>
-      </c>
+      <c r="B540" s="3"/>
+      <c r="C540" s="3"/>
       <c r="D540" s="3"/>
-      <c r="F540" t="s">
-        <v>425</v>
-      </c>
     </row>
     <row r="541" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B541" s="3"/>
-      <c r="C541" s="3"/>
-      <c r="D541" s="3"/>
+      <c r="A541" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B541" s="6">
+        <v>301</v>
+      </c>
+      <c r="C541" s="6">
+        <v>301</v>
+      </c>
+      <c r="D541" s="6"/>
+      <c r="G541" t="s">
+        <v>423</v>
+      </c>
     </row>
     <row r="542" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A542" s="2" t="s">
         <v>74</v>
       </c>
       <c r="B542" s="6">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C542" s="6">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D542" s="6"/>
       <c r="G542" t="s">
-        <v>427</v>
+        <v>440</v>
       </c>
     </row>
     <row r="543" spans="1:7" x14ac:dyDescent="0.25">
@@ -11637,14 +11639,14 @@
         <v>74</v>
       </c>
       <c r="B543" s="6">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C543" s="6">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D543" s="6"/>
       <c r="G543" t="s">
-        <v>444</v>
+        <v>460</v>
       </c>
     </row>
     <row r="544" spans="1:7" x14ac:dyDescent="0.25">
@@ -11652,14 +11654,14 @@
         <v>74</v>
       </c>
       <c r="B544" s="6">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C544" s="6">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D544" s="6"/>
       <c r="G544" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="545" spans="1:7" x14ac:dyDescent="0.25">
@@ -11667,14 +11669,14 @@
         <v>74</v>
       </c>
       <c r="B545" s="6">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C545" s="6">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D545" s="6"/>
       <c r="G545" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="546" spans="1:7" x14ac:dyDescent="0.25">
@@ -11682,10 +11684,10 @@
         <v>74</v>
       </c>
       <c r="B546" s="6">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C546" s="6">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D546" s="6"/>
       <c r="G546" t="s">
@@ -11697,14 +11699,14 @@
         <v>74</v>
       </c>
       <c r="B547" s="6">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C547" s="6">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D547" s="6"/>
       <c r="G547" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="548" spans="1:7" x14ac:dyDescent="0.25">
@@ -11712,14 +11714,14 @@
         <v>74</v>
       </c>
       <c r="B548" s="6">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C548" s="6">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D548" s="6"/>
       <c r="G548" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="549" spans="1:7" x14ac:dyDescent="0.25">
@@ -11727,14 +11729,14 @@
         <v>74</v>
       </c>
       <c r="B549" s="6">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C549" s="6">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D549" s="6"/>
       <c r="G549" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="550" spans="1:7" x14ac:dyDescent="0.25">
@@ -11742,14 +11744,14 @@
         <v>74</v>
       </c>
       <c r="B550" s="6">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C550" s="6">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D550" s="6"/>
       <c r="G550" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="551" spans="1:7" x14ac:dyDescent="0.25">
@@ -11757,14 +11759,14 @@
         <v>74</v>
       </c>
       <c r="B551" s="6">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C551" s="6">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D551" s="6"/>
       <c r="G551" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="552" spans="1:7" x14ac:dyDescent="0.25">
@@ -11772,14 +11774,14 @@
         <v>74</v>
       </c>
       <c r="B552" s="6">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C552" s="6">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D552" s="6"/>
       <c r="G552" t="s">
-        <v>484</v>
+        <v>559</v>
       </c>
     </row>
     <row r="553" spans="1:7" x14ac:dyDescent="0.25">
@@ -11787,10 +11789,10 @@
         <v>74</v>
       </c>
       <c r="B553" s="6">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C553" s="6">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D553" s="6"/>
       <c r="G553" t="s">
@@ -11802,14 +11804,14 @@
         <v>74</v>
       </c>
       <c r="B554" s="6">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C554" s="6">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D554" s="6"/>
       <c r="G554" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
     </row>
     <row r="555" spans="1:7" x14ac:dyDescent="0.25">
@@ -11817,14 +11819,14 @@
         <v>74</v>
       </c>
       <c r="B555" s="6">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C555" s="6">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D555" s="6"/>
       <c r="G555" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="556" spans="1:7" x14ac:dyDescent="0.25">
@@ -11832,14 +11834,14 @@
         <v>74</v>
       </c>
       <c r="B556" s="6">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C556" s="6">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D556" s="6"/>
       <c r="G556" t="s">
-        <v>571</v>
+        <v>541</v>
       </c>
     </row>
     <row r="557" spans="1:7" x14ac:dyDescent="0.25">
@@ -11847,14 +11849,14 @@
         <v>74</v>
       </c>
       <c r="B557" s="6">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C557" s="6">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D557" s="6"/>
       <c r="G557" t="s">
-        <v>545</v>
+        <v>435</v>
       </c>
     </row>
     <row r="558" spans="1:7" x14ac:dyDescent="0.25">
@@ -11862,14 +11864,14 @@
         <v>74</v>
       </c>
       <c r="B558" s="6">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C558" s="6">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D558" s="6"/>
       <c r="G558" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
     </row>
     <row r="559" spans="1:7" x14ac:dyDescent="0.25">
@@ -11877,14 +11879,14 @@
         <v>74</v>
       </c>
       <c r="B559" s="6">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C559" s="6">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D559" s="6"/>
       <c r="G559" t="s">
-        <v>436</v>
+        <v>507</v>
       </c>
     </row>
     <row r="560" spans="1:7" x14ac:dyDescent="0.25">
@@ -11892,14 +11894,14 @@
         <v>74</v>
       </c>
       <c r="B560" s="6">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C560" s="6">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D560" s="6"/>
       <c r="G560" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
     </row>
     <row r="561" spans="1:7" x14ac:dyDescent="0.25">
@@ -11907,14 +11909,14 @@
         <v>74</v>
       </c>
       <c r="B561" s="6">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C561" s="6">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D561" s="6"/>
       <c r="G561" t="s">
-        <v>521</v>
+        <v>571</v>
       </c>
     </row>
     <row r="562" spans="1:7" x14ac:dyDescent="0.25">
@@ -11922,14 +11924,14 @@
         <v>74</v>
       </c>
       <c r="B562" s="6">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C562" s="6">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D562" s="6"/>
       <c r="G562" t="s">
-        <v>575</v>
+        <v>495</v>
       </c>
     </row>
     <row r="563" spans="1:7" x14ac:dyDescent="0.25">
@@ -11937,14 +11939,14 @@
         <v>74</v>
       </c>
       <c r="B563" s="6">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C563" s="6">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D563" s="6"/>
       <c r="G563" t="s">
-        <v>499</v>
+        <v>446</v>
       </c>
     </row>
     <row r="564" spans="1:7" x14ac:dyDescent="0.25">
@@ -11952,14 +11954,14 @@
         <v>74</v>
       </c>
       <c r="B564" s="6">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C564" s="6">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D564" s="6"/>
       <c r="G564" t="s">
-        <v>450</v>
+        <v>526</v>
       </c>
     </row>
     <row r="565" spans="1:7" x14ac:dyDescent="0.25">
@@ -11967,14 +11969,14 @@
         <v>74</v>
       </c>
       <c r="B565" s="6">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C565" s="6">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D565" s="6"/>
       <c r="G565" t="s">
-        <v>530</v>
+        <v>544</v>
       </c>
     </row>
     <row r="566" spans="1:7" x14ac:dyDescent="0.25">
@@ -11982,14 +11984,14 @@
         <v>74</v>
       </c>
       <c r="B566" s="6">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C566" s="6">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D566" s="6"/>
       <c r="G566" t="s">
-        <v>548</v>
+        <v>494</v>
       </c>
     </row>
     <row r="567" spans="1:7" x14ac:dyDescent="0.25">
@@ -11997,14 +11999,14 @@
         <v>74</v>
       </c>
       <c r="B567" s="6">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C567" s="6">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D567" s="6"/>
       <c r="G567" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
     </row>
     <row r="568" spans="1:7" x14ac:dyDescent="0.25">
@@ -12012,14 +12014,14 @@
         <v>74</v>
       </c>
       <c r="B568" s="6">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C568" s="6">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D568" s="6"/>
       <c r="G568" t="s">
-        <v>497</v>
+        <v>546</v>
       </c>
     </row>
     <row r="569" spans="1:7" x14ac:dyDescent="0.25">
@@ -12027,14 +12029,14 @@
         <v>74</v>
       </c>
       <c r="B569" s="6">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C569" s="6">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D569" s="6"/>
       <c r="G569" t="s">
-        <v>550</v>
+        <v>485</v>
       </c>
     </row>
     <row r="570" spans="1:7" x14ac:dyDescent="0.25">
@@ -12042,14 +12044,14 @@
         <v>74</v>
       </c>
       <c r="B570" s="6">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C570" s="6">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D570" s="6"/>
       <c r="G570" t="s">
-        <v>489</v>
+        <v>547</v>
       </c>
     </row>
     <row r="571" spans="1:7" x14ac:dyDescent="0.25">
@@ -12057,14 +12059,14 @@
         <v>74</v>
       </c>
       <c r="B571" s="6">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C571" s="6">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D571" s="6"/>
       <c r="G571" t="s">
-        <v>551</v>
+        <v>457</v>
       </c>
     </row>
     <row r="572" spans="1:7" x14ac:dyDescent="0.25">
@@ -12072,14 +12074,14 @@
         <v>74</v>
       </c>
       <c r="B572" s="6">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C572" s="6">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D572" s="6"/>
       <c r="G572" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
     </row>
     <row r="573" spans="1:7" x14ac:dyDescent="0.25">
@@ -12087,14 +12089,14 @@
         <v>74</v>
       </c>
       <c r="B573" s="6">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C573" s="6">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D573" s="6"/>
       <c r="G573" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="574" spans="1:7" x14ac:dyDescent="0.25">
@@ -12102,14 +12104,14 @@
         <v>74</v>
       </c>
       <c r="B574" s="6">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C574" s="6">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D574" s="6"/>
       <c r="G574" t="s">
-        <v>462</v>
+        <v>395</v>
       </c>
     </row>
     <row r="575" spans="1:7" x14ac:dyDescent="0.25">
@@ -12117,14 +12119,14 @@
         <v>74</v>
       </c>
       <c r="B575" s="6">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C575" s="6">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D575" s="6"/>
       <c r="G575" t="s">
-        <v>399</v>
+        <v>461</v>
       </c>
     </row>
     <row r="576" spans="1:7" x14ac:dyDescent="0.25">
@@ -12132,14 +12134,14 @@
         <v>74</v>
       </c>
       <c r="B576" s="6">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C576" s="6">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D576" s="6"/>
       <c r="G576" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="577" spans="1:7" x14ac:dyDescent="0.25">
@@ -12147,10 +12149,10 @@
         <v>74</v>
       </c>
       <c r="B577" s="6">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C577" s="6">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D577" s="6"/>
       <c r="G577" t="s">
@@ -12162,14 +12164,14 @@
         <v>74</v>
       </c>
       <c r="B578" s="6">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C578" s="6">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D578" s="6"/>
       <c r="G578" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="579" spans="1:7" x14ac:dyDescent="0.25">
@@ -12177,14 +12179,14 @@
         <v>74</v>
       </c>
       <c r="B579" s="6">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C579" s="6">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D579" s="6"/>
       <c r="G579" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="580" spans="1:7" x14ac:dyDescent="0.25">
@@ -12192,14 +12194,14 @@
         <v>74</v>
       </c>
       <c r="B580" s="6">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C580" s="6">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D580" s="6"/>
       <c r="G580" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="581" spans="1:7" x14ac:dyDescent="0.25">
@@ -12207,14 +12209,14 @@
         <v>74</v>
       </c>
       <c r="B581" s="6">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C581" s="6">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D581" s="6"/>
       <c r="G581" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="582" spans="1:7" x14ac:dyDescent="0.25">
@@ -12222,14 +12224,14 @@
         <v>74</v>
       </c>
       <c r="B582" s="6">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C582" s="6">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D582" s="6"/>
       <c r="G582" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="583" spans="1:7" x14ac:dyDescent="0.25">
@@ -12237,14 +12239,14 @@
         <v>74</v>
       </c>
       <c r="B583" s="6">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C583" s="6">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D583" s="6"/>
       <c r="G583" t="s">
-        <v>485</v>
+        <v>561</v>
       </c>
     </row>
     <row r="584" spans="1:7" x14ac:dyDescent="0.25">
@@ -12252,10 +12254,10 @@
         <v>74</v>
       </c>
       <c r="B584" s="6">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C584" s="6">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D584" s="6"/>
       <c r="G584" t="s">
@@ -12267,14 +12269,14 @@
         <v>74</v>
       </c>
       <c r="B585" s="6">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C585" s="6">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D585" s="6"/>
       <c r="G585" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="586" spans="1:7" x14ac:dyDescent="0.25">
@@ -12282,14 +12284,14 @@
         <v>74</v>
       </c>
       <c r="B586" s="6">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C586" s="6">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D586" s="6"/>
       <c r="G586" t="s">
-        <v>572</v>
+        <v>428</v>
       </c>
     </row>
     <row r="587" spans="1:7" x14ac:dyDescent="0.25">
@@ -12297,14 +12299,14 @@
         <v>74</v>
       </c>
       <c r="B587" s="6">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C587" s="6">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D587" s="6"/>
       <c r="G587" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
     </row>
     <row r="588" spans="1:7" x14ac:dyDescent="0.25">
@@ -12312,14 +12314,14 @@
         <v>74</v>
       </c>
       <c r="B588" s="6">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C588" s="6">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D588" s="6"/>
       <c r="G588" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
     </row>
     <row r="589" spans="1:7" x14ac:dyDescent="0.25">
@@ -12327,14 +12329,14 @@
         <v>74</v>
       </c>
       <c r="B589" s="6">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C589" s="6">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D589" s="6"/>
       <c r="G589" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
     </row>
     <row r="590" spans="1:7" x14ac:dyDescent="0.25">
@@ -12342,14 +12344,14 @@
         <v>74</v>
       </c>
       <c r="B590" s="6">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C590" s="6">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D590" s="6"/>
       <c r="G590" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
     </row>
     <row r="591" spans="1:7" x14ac:dyDescent="0.25">
@@ -12357,14 +12359,14 @@
         <v>74</v>
       </c>
       <c r="B591" s="6">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C591" s="6">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D591" s="6"/>
       <c r="G591" t="s">
-        <v>456</v>
+        <v>503</v>
       </c>
     </row>
     <row r="592" spans="1:7" x14ac:dyDescent="0.25">
@@ -12372,14 +12374,14 @@
         <v>74</v>
       </c>
       <c r="B592" s="6">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C592" s="6">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D592" s="6"/>
       <c r="G592" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="593" spans="1:7" x14ac:dyDescent="0.25">
@@ -12387,14 +12389,14 @@
         <v>74</v>
       </c>
       <c r="B593" s="6">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C593" s="6">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D593" s="6"/>
       <c r="G593" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
     </row>
     <row r="594" spans="1:7" x14ac:dyDescent="0.25">
@@ -12402,14 +12404,14 @@
         <v>74</v>
       </c>
       <c r="B594" s="6">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C594" s="6">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D594" s="6"/>
       <c r="G594" t="s">
-        <v>512</v>
+        <v>530</v>
       </c>
     </row>
     <row r="595" spans="1:7" x14ac:dyDescent="0.25">
@@ -12417,14 +12419,14 @@
         <v>74</v>
       </c>
       <c r="B595" s="6">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C595" s="6">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D595" s="6"/>
       <c r="G595" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="596" spans="1:7" x14ac:dyDescent="0.25">
@@ -12432,14 +12434,14 @@
         <v>74</v>
       </c>
       <c r="B596" s="6">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C596" s="6">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D596" s="6"/>
       <c r="G596" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="597" spans="1:7" x14ac:dyDescent="0.25">
@@ -12447,14 +12449,14 @@
         <v>74</v>
       </c>
       <c r="B597" s="6">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C597" s="6">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D597" s="6"/>
       <c r="G597" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
     </row>
     <row r="598" spans="1:7" x14ac:dyDescent="0.25">
@@ -12462,14 +12464,14 @@
         <v>74</v>
       </c>
       <c r="B598" s="6">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C598" s="6">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D598" s="6"/>
       <c r="G598" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
     </row>
     <row r="599" spans="1:7" x14ac:dyDescent="0.25">
@@ -12477,14 +12479,14 @@
         <v>74</v>
       </c>
       <c r="B599" s="6">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C599" s="6">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D599" s="6"/>
       <c r="G599" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="600" spans="1:7" x14ac:dyDescent="0.25">
@@ -12492,14 +12494,14 @@
         <v>74</v>
       </c>
       <c r="B600" s="6">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C600" s="6">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D600" s="6"/>
       <c r="G600" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
     </row>
     <row r="601" spans="1:7" x14ac:dyDescent="0.25">
@@ -12507,14 +12509,14 @@
         <v>74</v>
       </c>
       <c r="B601" s="6">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C601" s="6">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D601" s="6"/>
       <c r="G601" t="s">
-        <v>541</v>
+        <v>466</v>
       </c>
     </row>
     <row r="602" spans="1:7" x14ac:dyDescent="0.25">
@@ -12522,14 +12524,14 @@
         <v>74</v>
       </c>
       <c r="B602" s="6">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C602" s="6">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D602" s="6"/>
       <c r="G602" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
     </row>
     <row r="603" spans="1:7" x14ac:dyDescent="0.25">
@@ -12537,14 +12539,14 @@
         <v>74</v>
       </c>
       <c r="B603" s="6">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C603" s="6">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D603" s="6"/>
       <c r="G603" t="s">
-        <v>469</v>
+        <v>502</v>
       </c>
     </row>
     <row r="604" spans="1:7" x14ac:dyDescent="0.25">
@@ -12552,14 +12554,14 @@
         <v>74</v>
       </c>
       <c r="B604" s="6">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C604" s="6">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D604" s="6"/>
       <c r="G604" t="s">
-        <v>506</v>
+        <v>436</v>
       </c>
     </row>
     <row r="605" spans="1:7" x14ac:dyDescent="0.25">
@@ -12567,14 +12569,14 @@
         <v>74</v>
       </c>
       <c r="B605" s="6">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C605" s="6">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D605" s="6"/>
       <c r="G605" t="s">
-        <v>440</v>
+        <v>488</v>
       </c>
     </row>
     <row r="606" spans="1:7" x14ac:dyDescent="0.25">
@@ -12582,14 +12584,14 @@
         <v>74</v>
       </c>
       <c r="B606" s="6">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C606" s="6">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D606" s="6"/>
       <c r="G606" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="607" spans="1:7" x14ac:dyDescent="0.25">
@@ -12597,14 +12599,14 @@
         <v>74</v>
       </c>
       <c r="B607" s="6">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C607" s="6">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D607" s="6"/>
       <c r="G607" t="s">
-        <v>493</v>
+        <v>442</v>
       </c>
     </row>
     <row r="608" spans="1:7" x14ac:dyDescent="0.25">
@@ -12612,14 +12614,14 @@
         <v>74</v>
       </c>
       <c r="B608" s="6">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C608" s="6">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D608" s="6"/>
       <c r="G608" t="s">
-        <v>446</v>
+        <v>557</v>
       </c>
     </row>
     <row r="609" spans="1:7" x14ac:dyDescent="0.25">
@@ -12627,14 +12629,14 @@
         <v>74</v>
       </c>
       <c r="B609" s="6">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C609" s="6">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D609" s="6"/>
       <c r="G609" t="s">
-        <v>561</v>
+        <v>516</v>
       </c>
     </row>
     <row r="610" spans="1:7" x14ac:dyDescent="0.25">
@@ -12642,14 +12644,14 @@
         <v>74</v>
       </c>
       <c r="B610" s="6">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C610" s="6">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D610" s="6"/>
       <c r="G610" t="s">
-        <v>520</v>
+        <v>438</v>
       </c>
     </row>
     <row r="611" spans="1:7" x14ac:dyDescent="0.25">
@@ -12657,14 +12659,14 @@
         <v>74</v>
       </c>
       <c r="B611" s="6">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C611" s="6">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D611" s="6"/>
       <c r="G611" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
     </row>
     <row r="612" spans="1:7" x14ac:dyDescent="0.25">
@@ -12672,14 +12674,14 @@
         <v>74</v>
       </c>
       <c r="B612" s="6">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C612" s="6">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D612" s="6"/>
       <c r="G612" t="s">
-        <v>443</v>
+        <v>497</v>
       </c>
     </row>
     <row r="613" spans="1:7" x14ac:dyDescent="0.25">
@@ -12687,14 +12689,14 @@
         <v>74</v>
       </c>
       <c r="B613" s="6">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C613" s="6">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D613" s="6"/>
       <c r="G613" t="s">
-        <v>501</v>
+        <v>443</v>
       </c>
     </row>
     <row r="614" spans="1:7" x14ac:dyDescent="0.25">
@@ -12702,14 +12704,14 @@
         <v>74</v>
       </c>
       <c r="B614" s="6">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C614" s="6">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D614" s="6"/>
       <c r="G614" t="s">
-        <v>447</v>
+        <v>505</v>
       </c>
     </row>
     <row r="615" spans="1:7" x14ac:dyDescent="0.25">
@@ -12717,14 +12719,14 @@
         <v>74</v>
       </c>
       <c r="B615" s="6">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C615" s="6">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D615" s="6"/>
       <c r="G615" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="616" spans="1:7" x14ac:dyDescent="0.25">
@@ -12732,14 +12734,14 @@
         <v>74</v>
       </c>
       <c r="B616" s="6">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C616" s="6">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D616" s="6"/>
       <c r="G616" t="s">
-        <v>510</v>
+        <v>496</v>
       </c>
     </row>
     <row r="617" spans="1:7" x14ac:dyDescent="0.25">
@@ -12747,14 +12749,14 @@
         <v>74</v>
       </c>
       <c r="B617" s="6">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C617" s="6">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D617" s="6"/>
       <c r="G617" t="s">
-        <v>500</v>
+        <v>533</v>
       </c>
     </row>
     <row r="618" spans="1:7" x14ac:dyDescent="0.25">
@@ -12762,14 +12764,14 @@
         <v>74</v>
       </c>
       <c r="B618" s="6">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C618" s="6">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D618" s="6"/>
       <c r="G618" t="s">
-        <v>537</v>
+        <v>518</v>
       </c>
     </row>
     <row r="619" spans="1:7" x14ac:dyDescent="0.25">
@@ -12777,14 +12779,14 @@
         <v>74</v>
       </c>
       <c r="B619" s="6">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C619" s="6">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D619" s="6"/>
       <c r="G619" t="s">
-        <v>522</v>
+        <v>539</v>
       </c>
     </row>
     <row r="620" spans="1:7" x14ac:dyDescent="0.25">
@@ -12792,14 +12794,14 @@
         <v>74</v>
       </c>
       <c r="B620" s="6">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C620" s="6">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D620" s="6"/>
       <c r="G620" t="s">
-        <v>543</v>
+        <v>511</v>
       </c>
     </row>
     <row r="621" spans="1:7" x14ac:dyDescent="0.25">
@@ -12807,14 +12809,14 @@
         <v>74</v>
       </c>
       <c r="B621" s="6">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C621" s="6">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D621" s="6"/>
       <c r="G621" t="s">
-        <v>515</v>
+        <v>554</v>
       </c>
     </row>
     <row r="622" spans="1:7" x14ac:dyDescent="0.25">
@@ -12822,14 +12824,14 @@
         <v>74</v>
       </c>
       <c r="B622" s="6">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C622" s="6">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D622" s="6"/>
       <c r="G622" t="s">
-        <v>558</v>
+        <v>519</v>
       </c>
     </row>
     <row r="623" spans="1:7" x14ac:dyDescent="0.25">
@@ -12837,14 +12839,14 @@
         <v>74</v>
       </c>
       <c r="B623" s="6">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C623" s="6">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D623" s="6"/>
       <c r="G623" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="624" spans="1:7" x14ac:dyDescent="0.25">
@@ -12852,14 +12854,14 @@
         <v>74</v>
       </c>
       <c r="B624" s="6">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C624" s="6">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D624" s="6"/>
       <c r="G624" t="s">
-        <v>524</v>
+        <v>487</v>
       </c>
     </row>
     <row r="625" spans="1:7" x14ac:dyDescent="0.25">
@@ -12867,14 +12869,14 @@
         <v>74</v>
       </c>
       <c r="B625" s="6">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C625" s="6">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D625" s="6"/>
       <c r="G625" t="s">
-        <v>491</v>
+        <v>558</v>
       </c>
     </row>
     <row r="626" spans="1:7" x14ac:dyDescent="0.25">
@@ -12882,14 +12884,14 @@
         <v>74</v>
       </c>
       <c r="B626" s="6">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C626" s="6">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D626" s="6"/>
       <c r="G626" t="s">
-        <v>562</v>
+        <v>521</v>
       </c>
     </row>
     <row r="627" spans="1:7" x14ac:dyDescent="0.25">
@@ -12897,14 +12899,14 @@
         <v>74</v>
       </c>
       <c r="B627" s="6">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C627" s="6">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D627" s="6"/>
       <c r="G627" t="s">
-        <v>525</v>
+        <v>540</v>
       </c>
     </row>
     <row r="628" spans="1:7" x14ac:dyDescent="0.25">
@@ -12912,14 +12914,14 @@
         <v>74</v>
       </c>
       <c r="B628" s="6">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C628" s="6">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D628" s="6"/>
       <c r="G628" t="s">
-        <v>544</v>
+        <v>527</v>
       </c>
     </row>
     <row r="629" spans="1:7" x14ac:dyDescent="0.25">
@@ -12927,14 +12929,14 @@
         <v>74</v>
       </c>
       <c r="B629" s="6">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C629" s="6">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D629" s="6"/>
       <c r="G629" t="s">
-        <v>531</v>
+        <v>492</v>
       </c>
     </row>
     <row r="630" spans="1:7" x14ac:dyDescent="0.25">
@@ -12942,14 +12944,14 @@
         <v>74</v>
       </c>
       <c r="B630" s="6">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C630" s="6">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D630" s="6"/>
       <c r="G630" t="s">
-        <v>496</v>
+        <v>431</v>
       </c>
     </row>
     <row r="631" spans="1:7" x14ac:dyDescent="0.25">
@@ -12957,14 +12959,14 @@
         <v>74</v>
       </c>
       <c r="B631" s="6">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C631" s="6">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D631" s="6"/>
       <c r="G631" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
     </row>
     <row r="632" spans="1:7" x14ac:dyDescent="0.25">
@@ -12972,14 +12974,14 @@
         <v>74</v>
       </c>
       <c r="B632" s="6">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C632" s="6">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D632" s="6"/>
       <c r="G632" t="s">
-        <v>428</v>
+        <v>482</v>
       </c>
     </row>
     <row r="633" spans="1:7" x14ac:dyDescent="0.25">
@@ -12987,14 +12989,14 @@
         <v>74</v>
       </c>
       <c r="B633" s="6">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C633" s="6">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D633" s="6"/>
       <c r="G633" t="s">
-        <v>486</v>
+        <v>504</v>
       </c>
     </row>
     <row r="634" spans="1:7" x14ac:dyDescent="0.25">
@@ -13002,14 +13004,14 @@
         <v>74</v>
       </c>
       <c r="B634" s="6">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C634" s="6">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D634" s="6"/>
       <c r="G634" t="s">
-        <v>508</v>
+        <v>445</v>
       </c>
     </row>
     <row r="635" spans="1:7" x14ac:dyDescent="0.25">
@@ -13017,14 +13019,14 @@
         <v>74</v>
       </c>
       <c r="B635" s="6">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C635" s="6">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D635" s="6"/>
       <c r="G635" t="s">
-        <v>449</v>
+        <v>425</v>
       </c>
     </row>
     <row r="636" spans="1:7" x14ac:dyDescent="0.25">
@@ -13032,14 +13034,14 @@
         <v>74</v>
       </c>
       <c r="B636" s="6">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C636" s="6">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D636" s="6"/>
       <c r="G636" t="s">
-        <v>429</v>
+        <v>551</v>
       </c>
     </row>
     <row r="637" spans="1:7" x14ac:dyDescent="0.25">
@@ -13047,14 +13049,14 @@
         <v>74</v>
       </c>
       <c r="B637" s="6">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C637" s="6">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D637" s="6"/>
       <c r="G637" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
     </row>
     <row r="638" spans="1:7" x14ac:dyDescent="0.25">
@@ -13062,14 +13064,14 @@
         <v>74</v>
       </c>
       <c r="B638" s="6">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C638" s="6">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D638" s="6"/>
       <c r="G638" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
     </row>
     <row r="639" spans="1:7" x14ac:dyDescent="0.25">
@@ -13077,29 +13079,28 @@
         <v>74</v>
       </c>
       <c r="B639" s="6">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C639" s="6">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D639" s="6"/>
       <c r="G639" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
     </row>
     <row r="640" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A640" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B640" s="6">
-        <v>399</v>
-      </c>
-      <c r="C640" s="6">
-        <v>399</v>
-      </c>
-      <c r="D640" s="6"/>
+      <c r="B640" s="4">
+        <v>400</v>
+      </c>
+      <c r="C640" s="4">
+        <v>400</v>
+      </c>
       <c r="G640" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="641" spans="1:7" x14ac:dyDescent="0.25">
@@ -13107,13 +13108,13 @@
         <v>74</v>
       </c>
       <c r="B641" s="4">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C641" s="4">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G641" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
     </row>
     <row r="642" spans="1:7" x14ac:dyDescent="0.25">
@@ -13121,13 +13122,13 @@
         <v>74</v>
       </c>
       <c r="B642" s="4">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C642" s="4">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G642" t="s">
-        <v>552</v>
+        <v>426</v>
       </c>
     </row>
     <row r="643" spans="1:7" x14ac:dyDescent="0.25">
@@ -13135,13 +13136,13 @@
         <v>74</v>
       </c>
       <c r="B643" s="4">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C643" s="4">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G643" t="s">
-        <v>430</v>
+        <v>529</v>
       </c>
     </row>
     <row r="644" spans="1:7" x14ac:dyDescent="0.25">
@@ -13149,13 +13150,13 @@
         <v>74</v>
       </c>
       <c r="B644" s="4">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C644" s="4">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="G644" t="s">
-        <v>533</v>
+        <v>514</v>
       </c>
     </row>
     <row r="645" spans="1:7" x14ac:dyDescent="0.25">
@@ -13163,13 +13164,13 @@
         <v>74</v>
       </c>
       <c r="B645" s="4">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C645" s="4">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="G645" t="s">
-        <v>518</v>
+        <v>483</v>
       </c>
     </row>
     <row r="646" spans="1:7" x14ac:dyDescent="0.25">
@@ -13177,13 +13178,13 @@
         <v>74</v>
       </c>
       <c r="B646" s="4">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C646" s="4">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="G646" t="s">
-        <v>487</v>
+        <v>427</v>
       </c>
     </row>
     <row r="647" spans="1:7" x14ac:dyDescent="0.25">
@@ -13191,13 +13192,13 @@
         <v>74</v>
       </c>
       <c r="B647" s="4">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C647" s="4">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="G647" t="s">
-        <v>431</v>
+        <v>447</v>
       </c>
     </row>
     <row r="648" spans="1:7" x14ac:dyDescent="0.25">
@@ -13205,13 +13206,13 @@
         <v>74</v>
       </c>
       <c r="B648" s="4">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C648" s="4">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="G648" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="649" spans="1:7" x14ac:dyDescent="0.25">
@@ -13219,13 +13220,13 @@
         <v>74</v>
       </c>
       <c r="B649" s="4">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C649" s="4">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G649" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
     </row>
     <row r="650" spans="1:7" x14ac:dyDescent="0.25">
@@ -13233,13 +13234,13 @@
         <v>74</v>
       </c>
       <c r="B650" s="4">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C650" s="4">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G650" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="651" spans="1:7" x14ac:dyDescent="0.25">
@@ -13247,13 +13248,13 @@
         <v>74</v>
       </c>
       <c r="B651" s="4">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C651" s="4">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="G651" t="s">
-        <v>454</v>
+        <v>484</v>
       </c>
     </row>
     <row r="652" spans="1:7" x14ac:dyDescent="0.25">
@@ -13261,13 +13262,13 @@
         <v>74</v>
       </c>
       <c r="B652" s="4">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C652" s="4">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G652" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="653" spans="1:7" x14ac:dyDescent="0.25">
@@ -13275,13 +13276,13 @@
         <v>74</v>
       </c>
       <c r="B653" s="4">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C653" s="4">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="G653" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="654" spans="1:7" x14ac:dyDescent="0.25">
@@ -13289,13 +13290,13 @@
         <v>74</v>
       </c>
       <c r="B654" s="4">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C654" s="4">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G654" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="655" spans="1:7" x14ac:dyDescent="0.25">
@@ -13303,13 +13304,13 @@
         <v>74</v>
       </c>
       <c r="B655" s="4">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C655" s="4">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G655" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
     </row>
     <row r="656" spans="1:7" x14ac:dyDescent="0.25">
@@ -13317,13 +13318,13 @@
         <v>74</v>
       </c>
       <c r="B656" s="4">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C656" s="4">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="G656" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
     </row>
     <row r="657" spans="1:7" x14ac:dyDescent="0.25">
@@ -13331,13 +13332,13 @@
         <v>74</v>
       </c>
       <c r="B657" s="4">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C657" s="4">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="G657" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
     <row r="658" spans="1:7" x14ac:dyDescent="0.25">
@@ -13345,13 +13346,13 @@
         <v>74</v>
       </c>
       <c r="B658" s="4">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C658" s="4">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G658" t="s">
-        <v>526</v>
+        <v>545</v>
       </c>
     </row>
     <row r="659" spans="1:7" x14ac:dyDescent="0.25">
@@ -13359,13 +13360,13 @@
         <v>74</v>
       </c>
       <c r="B659" s="4">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C659" s="4">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G659" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
     </row>
     <row r="660" spans="1:7" x14ac:dyDescent="0.25">
@@ -13373,13 +13374,13 @@
         <v>74</v>
       </c>
       <c r="B660" s="4">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C660" s="4">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="G660" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
     </row>
     <row r="661" spans="1:7" x14ac:dyDescent="0.25">
@@ -13387,10 +13388,10 @@
         <v>74</v>
       </c>
       <c r="B661" s="4">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C661" s="4">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G661" t="s">
         <v>560</v>
@@ -13401,13 +13402,13 @@
         <v>74</v>
       </c>
       <c r="B662" s="4">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C662" s="4">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="G662" t="s">
-        <v>564</v>
+        <v>459</v>
       </c>
     </row>
     <row r="663" spans="1:7" x14ac:dyDescent="0.25">
@@ -13415,13 +13416,13 @@
         <v>74</v>
       </c>
       <c r="B663" s="4">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C663" s="4">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="G663" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
     </row>
     <row r="664" spans="1:7" x14ac:dyDescent="0.25">
@@ -13429,13 +13430,13 @@
         <v>74</v>
       </c>
       <c r="B664" s="4">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C664" s="4">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G664" t="s">
-        <v>460</v>
+        <v>473</v>
       </c>
     </row>
     <row r="665" spans="1:7" x14ac:dyDescent="0.25">
@@ -13443,13 +13444,13 @@
         <v>74</v>
       </c>
       <c r="B665" s="4">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C665" s="4">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="G665" t="s">
-        <v>477</v>
+        <v>454</v>
       </c>
     </row>
     <row r="666" spans="1:7" x14ac:dyDescent="0.25">
@@ -13457,13 +13458,13 @@
         <v>74</v>
       </c>
       <c r="B666" s="4">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C666" s="4">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G666" t="s">
-        <v>458</v>
+        <v>422</v>
       </c>
     </row>
     <row r="667" spans="1:7" x14ac:dyDescent="0.25">
@@ -13471,13 +13472,13 @@
         <v>74</v>
       </c>
       <c r="B667" s="4">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C667" s="4">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G667" t="s">
-        <v>426</v>
+        <v>478</v>
       </c>
     </row>
     <row r="668" spans="1:7" x14ac:dyDescent="0.25">
@@ -13485,13 +13486,13 @@
         <v>74</v>
       </c>
       <c r="B668" s="4">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C668" s="4">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G668" t="s">
-        <v>482</v>
+        <v>566</v>
       </c>
     </row>
     <row r="669" spans="1:7" x14ac:dyDescent="0.25">
@@ -13499,13 +13500,13 @@
         <v>74</v>
       </c>
       <c r="B669" s="4">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C669" s="4">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="G669" t="s">
-        <v>570</v>
+        <v>463</v>
       </c>
     </row>
     <row r="670" spans="1:7" x14ac:dyDescent="0.25">
@@ -13513,13 +13514,13 @@
         <v>74</v>
       </c>
       <c r="B670" s="4">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C670" s="4">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G670" t="s">
-        <v>467</v>
+        <v>433</v>
       </c>
     </row>
     <row r="671" spans="1:7" x14ac:dyDescent="0.25">
@@ -13527,13 +13528,13 @@
         <v>74</v>
       </c>
       <c r="B671" s="4">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C671" s="4">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="G671" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="672" spans="1:7" x14ac:dyDescent="0.25">
@@ -13541,13 +13542,13 @@
         <v>74</v>
       </c>
       <c r="B672" s="4">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C672" s="4">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G672" t="s">
-        <v>438</v>
+        <v>562</v>
       </c>
     </row>
     <row r="673" spans="1:7" x14ac:dyDescent="0.25">
@@ -13555,13 +13556,13 @@
         <v>74</v>
       </c>
       <c r="B673" s="4">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C673" s="4">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G673" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
     </row>
     <row r="674" spans="1:7" x14ac:dyDescent="0.25">
@@ -13569,13 +13570,13 @@
         <v>74</v>
       </c>
       <c r="B674" s="4">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C674" s="4">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G674" t="s">
-        <v>573</v>
+        <v>455</v>
       </c>
     </row>
     <row r="675" spans="1:7" x14ac:dyDescent="0.25">
@@ -13583,13 +13584,13 @@
         <v>74</v>
       </c>
       <c r="B675" s="4">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C675" s="4">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G675" t="s">
-        <v>459</v>
+        <v>444</v>
       </c>
     </row>
     <row r="676" spans="1:7" x14ac:dyDescent="0.25">
@@ -13597,13 +13598,13 @@
         <v>74</v>
       </c>
       <c r="B676" s="4">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C676" s="4">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="G676" t="s">
-        <v>448</v>
+        <v>513</v>
       </c>
     </row>
     <row r="677" spans="1:7" x14ac:dyDescent="0.25">
@@ -13611,13 +13612,13 @@
         <v>74</v>
       </c>
       <c r="B677" s="4">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C677" s="4">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G677" t="s">
-        <v>517</v>
+        <v>532</v>
       </c>
     </row>
     <row r="678" spans="1:7" x14ac:dyDescent="0.25">
@@ -13625,13 +13626,13 @@
         <v>74</v>
       </c>
       <c r="B678" s="4">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C678" s="4">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="G678" t="s">
-        <v>536</v>
+        <v>510</v>
       </c>
     </row>
     <row r="679" spans="1:7" x14ac:dyDescent="0.25">
@@ -13639,13 +13640,13 @@
         <v>74</v>
       </c>
       <c r="B679" s="4">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C679" s="4">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="G679" t="s">
-        <v>514</v>
+        <v>524</v>
       </c>
     </row>
     <row r="680" spans="1:7" x14ac:dyDescent="0.25">
@@ -13653,13 +13654,13 @@
         <v>74</v>
       </c>
       <c r="B680" s="4">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C680" s="4">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="G680" t="s">
-        <v>528</v>
+        <v>486</v>
       </c>
     </row>
     <row r="681" spans="1:7" x14ac:dyDescent="0.25">
@@ -13667,13 +13668,13 @@
         <v>74</v>
       </c>
       <c r="B681" s="4">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C681" s="4">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="G681" t="s">
-        <v>490</v>
+        <v>528</v>
       </c>
     </row>
     <row r="682" spans="1:7" x14ac:dyDescent="0.25">
@@ -13681,13 +13682,13 @@
         <v>74</v>
       </c>
       <c r="B682" s="4">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C682" s="4">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="G682" t="s">
-        <v>532</v>
+        <v>501</v>
       </c>
     </row>
     <row r="683" spans="1:7" x14ac:dyDescent="0.25">
@@ -13695,13 +13696,13 @@
         <v>74</v>
       </c>
       <c r="B683" s="4">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C683" s="4">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="G683" t="s">
-        <v>505</v>
+        <v>542</v>
       </c>
     </row>
     <row r="684" spans="1:7" x14ac:dyDescent="0.25">
@@ -13709,13 +13710,13 @@
         <v>74</v>
       </c>
       <c r="B684" s="4">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C684" s="4">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G684" t="s">
-        <v>546</v>
+        <v>437</v>
       </c>
     </row>
     <row r="685" spans="1:7" x14ac:dyDescent="0.25">
@@ -13723,13 +13724,13 @@
         <v>74</v>
       </c>
       <c r="B685" s="4">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C685" s="4">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G685" t="s">
-        <v>441</v>
+        <v>525</v>
       </c>
     </row>
     <row r="686" spans="1:7" x14ac:dyDescent="0.25">
@@ -13737,13 +13738,13 @@
         <v>74</v>
       </c>
       <c r="B686" s="4">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C686" s="4">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="G686" t="s">
-        <v>529</v>
+        <v>543</v>
       </c>
     </row>
     <row r="687" spans="1:7" x14ac:dyDescent="0.25">
@@ -13751,13 +13752,13 @@
         <v>74</v>
       </c>
       <c r="B687" s="4">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C687" s="4">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G687" t="s">
-        <v>547</v>
+        <v>512</v>
       </c>
     </row>
     <row r="688" spans="1:7" x14ac:dyDescent="0.25">
@@ -13765,13 +13766,13 @@
         <v>74</v>
       </c>
       <c r="B688" s="4">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C688" s="4">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="G688" t="s">
-        <v>516</v>
+        <v>441</v>
       </c>
     </row>
     <row r="689" spans="1:7" x14ac:dyDescent="0.25">
@@ -13779,13 +13780,13 @@
         <v>74</v>
       </c>
       <c r="B689" s="4">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C689" s="4">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G689" t="s">
-        <v>445</v>
+        <v>498</v>
       </c>
     </row>
     <row r="690" spans="1:7" x14ac:dyDescent="0.25">
@@ -13793,31 +13794,17 @@
         <v>74</v>
       </c>
       <c r="B690" s="4">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C690" s="4">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="G690" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="691" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A691" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B691" s="4">
-        <v>450</v>
-      </c>
-      <c r="C691" s="4">
-        <v>450</v>
-      </c>
-      <c r="G691" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="714" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G714" s="13"/>
+        <v>523</v>
+      </c>
+    </row>
+    <row r="713" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G713" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -13852,10 +13839,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>279</v>
+        <v>574</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>278</v>
+        <v>575</v>
       </c>
       <c r="C2" t="s">
         <v>68</v>
